--- a/tame_output/ON/bt/strategyON_20240517.xlsx
+++ b/tame_output/ON/bt/strategyON_20240517.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>46.0%</t>
         </is>
       </c>
     </row>
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.7%</t>
+          <t>110.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.3%</t>
+          <t>-73.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>445.1%</t>
+          <t>448.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-10.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-576.8%</t>
+          <t>-576.3%</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>264.4%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>100.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-247.2%</t>
+          <t>-247.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-26.7%</t>
+          <t>-26.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.6%</t>
+          <t>-32.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-90.1%</t>
+          <t>-101.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-247.7%</t>
+          <t>-245.7%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-165.1%</t>
+          <t>-163.9%</t>
         </is>
       </c>
     </row>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330522</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108639</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923088</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240574</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081565</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.33147827443261</v>
+        <v>-10.33643685794989</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9573277397306494</v>
+        <v>-0.959311173137559</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.500971549953501</v>
+        <v>-2.505930133470775</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.675037064384042</v>
+        <v>1.672061914273678</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.06764140722854</v>
+        <v>-10.07259999074582</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8616764741619298</v>
+        <v>-0.8636599075688394</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.500971549953501</v>
+        <v>-2.505930133470775</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.665153583071135</v>
+        <v>1.662178432960771</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.800399606360145</v>
+        <v>-9.805358189877419</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7566143143139441</v>
+        <v>-0.7585977477208536</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.500971549953501</v>
+        <v>-2.505930133470775</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.663319022571761</v>
+        <v>1.660343872461397</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781946</v>
+        <v>3.784680945781945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.702492567683654</v>
+        <v>-9.707451151200928</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7177518138168089</v>
+        <v>-0.7197352472237184</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.432985800092944</v>
+        <v>-2.437944383610218</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.703810157514634</v>
+        <v>1.70083500740427</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.678539026707696</v>
+        <v>-9.68349761022497</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7075018912809319</v>
+        <v>-0.7094853246878414</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.409032259116987</v>
+        <v>-2.413990842634261</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.718850788245702</v>
+        <v>1.715875638135338</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487771</v>
+        <v>3.78930753648777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.414479088384899</v>
+        <v>-9.419437671902173</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6151382321135652</v>
+        <v>-0.6171216655204748</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.144972320794191</v>
+        <v>-2.149930904311465</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.864026435077628</v>
+        <v>1.861051284967263</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.707399464880062</v>
+        <v>-8.712358048397336</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3350934163719312</v>
+        <v>-0.3370768497788408</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.144972320794191</v>
+        <v>-2.149930904311465</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.861239401417327</v>
+        <v>1.858264251306962</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.667215166513872</v>
+        <v>-8.672173750031146</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3186760731376137</v>
+        <v>-0.3206595065445232</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.104788022428</v>
+        <v>-2.109746605945274</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.885693604324883</v>
+        <v>1.882718454214518</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.587145370976067</v>
+        <v>-8.592103954493341</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2872813337017348</v>
+        <v>-0.2892647671086443</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.024718226890196</v>
+        <v>-2.02967681040747</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.933102302868322</v>
+        <v>1.930127152757958</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.353664148746468</v>
+        <v>-8.358622732263743</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1859644159720428</v>
+        <v>-0.1879478493789533</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.791237004660597</v>
+        <v>-1.796195588177871</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.081115465043934</v>
+        <v>2.078140314933569</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.203997757738954</v>
+        <v>-8.208956341256229</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1289900698819961</v>
+        <v>-0.1309735032889066</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.698333513418061</v>
+        <v>-1.703292096935335</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.133965349476496</v>
+        <v>2.130990199366131</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.071722284108066</v>
+        <v>-8.076680867625342</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.08071239368261418</v>
+        <v>-0.08269582708952461</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.566058039787175</v>
+        <v>-1.571016623304449</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.208698120402055</v>
+        <v>2.205722970291691</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.881122609434914</v>
+        <v>-7.886081192952189</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.001657463125716685</v>
+        <v>-0.00364089653262667</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.375458365114022</v>
+        <v>-1.380416948631296</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.325872985893583</v>
+        <v>2.322897835783219</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.632122810751333</v>
+        <v>-7.637081394268608</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1108487975713746</v>
+        <v>0.1088653641644641</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.375458365114022</v>
+        <v>-1.380416948631296</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.338779327117242</v>
+        <v>2.335804177006878</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.737712800524437</v>
+        <v>-7.742671384041713</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.05936312793708609</v>
+        <v>-0.06134656134399608</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.481048354887126</v>
+        <v>-1.4860069384044</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.147449403654161</v>
+        <v>2.144474253543796</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.756447702643034</v>
+        <v>-7.76140628616031</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.01831274690743845</v>
+        <v>-0.02029618031434843</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.481048354887126</v>
+        <v>-1.4860069384044</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.195993745531247</v>
+        <v>2.193018595420883</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.608507661235435</v>
+        <v>-7.61346624475271</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.0790156530325663</v>
+        <v>-0.08099908643947629</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.460727438978569</v>
+        <v>-1.465686022495843</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.088307372388214</v>
+        <v>2.08533222227785</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.584279024846462</v>
+        <v>-7.589237608363738</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.07803818473045521</v>
+        <v>-0.08002161813736564</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.436498802589596</v>
+        <v>-1.44145738610687</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.094130567968119</v>
+        <v>2.091155417857755</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.540730618075772</v>
+        <v>-7.545689201593047</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.06757943411727219</v>
+        <v>-0.06956286752418261</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.436498802589596</v>
+        <v>-1.44145738610687</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.087169955873026</v>
+        <v>2.084194805762662</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.298582224621914</v>
+        <v>-7.303540808139189</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.04374227764541416</v>
+        <v>0.04175884423850373</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.436498802589596</v>
+        <v>-1.44145738610687</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.101632310254169</v>
+        <v>2.098657160143805</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.235352852853565</v>
+        <v>-7.240311436370841</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.06356614681194817</v>
+        <v>0.06158271340503818</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.436498802589596</v>
+        <v>-1.44145738610687</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.096164430713364</v>
+        <v>2.093189280603</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.112061718036434</v>
+        <v>-7.11702030155371</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1103806947493777</v>
+        <v>0.1083972613424673</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.313207667772466</v>
+        <v>-1.31816625128974</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.167637205614219</v>
+        <v>2.164662055503855</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.090912519132991</v>
+        <v>-7.095871102650267</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1265413525480801</v>
+        <v>0.1245579191411696</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.292058468869023</v>
+        <v>-1.297017052386296</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.188027703193611</v>
+        <v>2.185052553083247</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.847147077149547</v>
+        <v>-6.852105660666822</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2198282376885086</v>
+        <v>0.2178448042815981</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.292058468869023</v>
+        <v>-1.297017052386296</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.183808411540661</v>
+        <v>2.180833261430297</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.700250049431677</v>
+        <v>-6.705208632948953</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2807113626956723</v>
+        <v>0.2787279292887623</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.244400226890435</v>
+        <v>-1.249358810407708</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.21452767064783</v>
+        <v>2.211552520537466</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.450399655482602</v>
+        <v>-6.455358238999878</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3733935952590044</v>
+        <v>0.371410161852094</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.244400226890435</v>
+        <v>-1.249358810407708</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.207269745631532</v>
+        <v>2.204294595521168</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.27450756301517</v>
+        <v>-6.279466146532446</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4473495557666261</v>
+        <v>0.4453661223597156</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.244400226890435</v>
+        <v>-1.249358810407708</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.210868869152181</v>
+        <v>2.207893719041817</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.103061099992707</v>
+        <v>-6.108019683509982</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.529255647030165</v>
+        <v>0.5272722136232546</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.072953763867972</v>
+        <v>-1.077912347385245</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.327064253020212</v>
+        <v>2.324089102909848</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.878028100323884</v>
+        <v>-5.88298668384116</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6182893245139911</v>
+        <v>0.6163058911070811</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8479207641991487</v>
+        <v>-0.8528793477164226</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.461104530437803</v>
+        <v>2.458129380327439</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.814392358089949</v>
+        <v>-5.819350941607225</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6484384224618824</v>
+        <v>0.646454989054972</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7842850219652142</v>
+        <v>-0.7892436054824881</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.503980776832481</v>
+        <v>2.501005626722117</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.721392316884051</v>
+        <v>-5.726350900401327</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6668326977280374</v>
+        <v>0.664849264321127</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7842850219652142</v>
+        <v>-0.7892436054824881</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.485175035616277</v>
+        <v>2.482199885505913</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.480961820079191</v>
+        <v>-5.485920403596467</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7647479730748588</v>
+        <v>0.7627645396679483</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5438545251603539</v>
+        <v>-0.5488131086776278</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.63117641032407</v>
+        <v>2.628201260213706</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.408719251907996</v>
+        <v>-5.413677835425272</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7975743141781568</v>
+        <v>0.7955908807712464</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5438545251603539</v>
+        <v>-0.5488131086776278</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.63510572415889</v>
+        <v>2.632130574048526</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.292779402282811</v>
+        <v>-5.297737985800087</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8446288379455709</v>
+        <v>0.8426454045386609</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.46703279414423</v>
+        <v>-0.4719913776615039</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.681877346685905</v>
+        <v>2.678902196575541</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.050123813859647</v>
+        <v>-5.055082397376923</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.93868914453483</v>
+        <v>0.9367057111279196</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.46703279414423</v>
+        <v>-0.4719913776615039</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.678875417905898</v>
+        <v>2.675900267795534</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.830103015822637</v>
+        <v>-4.835061599339912</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.028276500760248</v>
+        <v>1.026293067353338</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3258129490762498</v>
+        <v>-0.3307715325935237</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.7651863619573</v>
+        <v>2.762211211846936</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.697235326759359</v>
+        <v>-4.702193910276635</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.097317759187383</v>
+        <v>1.095334325780472</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3258129490762498</v>
+        <v>-0.3307715325935237</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.781080544759124</v>
+        <v>2.778105394648759</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.537720223239989</v>
+        <v>-4.542678806757265</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.162269645035432</v>
+        <v>1.160286211628522</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1662978455568799</v>
+        <v>-0.1712564290741537</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.877935451311048</v>
+        <v>2.874960301200683</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.393048078140252</v>
+        <v>-4.398006661657528</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.230226605636767</v>
+        <v>1.228243172229857</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.02162570045714246</v>
+        <v>-0.02658428397441631</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.97482684093233</v>
+        <v>2.971851690821966</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.452922905497944</v>
+        <v>-4.45788148901522</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.192314166095116</v>
+        <v>1.190330732688206</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.08150052781483458</v>
+        <v>-0.08645911133210843</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.924939435919141</v>
+        <v>2.921964285808776</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.366123407718936</v>
+        <v>-4.371081991236212</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.249434458529286</v>
+        <v>1.247451025122375</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.08150052781483458</v>
+        <v>-0.08645911133210843</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.947339929241707</v>
+        <v>2.944364779131342</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.368593114180742</v>
+        <v>-4.373551697698018</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.248518977317975</v>
+        <v>1.246535543911065</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.08397023427664074</v>
+        <v>-0.08892881779391459</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.945930506738035</v>
+        <v>2.942955356627671</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.436963300504752</v>
+        <v>-4.441921884022028</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.232177825263073</v>
+        <v>1.230194391856163</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.0746945352404258</v>
+        <v>-0.07965311875769965</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.962502848634466</v>
+        <v>2.959527698524102</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.315546870878276</v>
+        <v>-4.320505454395551</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.271181105745555</v>
+        <v>1.269197672338645</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.0746945352404258</v>
+        <v>-0.07965311875769965</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.952939557266357</v>
+        <v>2.949964407155993</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.346540030206981</v>
+        <v>-4.351498613724257</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.08349340705446</v>
+        <v>1.08150997364755</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.0746945352404258</v>
+        <v>-0.07965311875769965</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.777649122306744</v>
+        <v>2.77467397219638</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.171065770414511</v>
+        <v>-4.176024353931787</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.158250342963235</v>
+        <v>1.156266909556325</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.0746945352404258</v>
+        <v>-0.07965311875769965</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.782216354298532</v>
+        <v>2.779241204188168</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.28200202305576</v>
+        <v>-4.286960606573036</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.089617870667943</v>
+        <v>1.087634437261033</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.0746945352404258</v>
+        <v>-0.07965311875769965</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.757958383059739</v>
+        <v>2.754983232949375</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.485028600598993</v>
+        <v>-4.489987184116269</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.011538624870555</v>
+        <v>1.009555191463645</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2777211127836592</v>
+        <v>-0.282679696300933</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.639273821753704</v>
+        <v>2.63629867164334</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.3271030016637</v>
+        <v>-4.332061585180976</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.084881250876805</v>
+        <v>1.082897817469894</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2777211127836592</v>
+        <v>-0.282679696300933</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.649446208185837</v>
+        <v>2.646471058075472</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.240859538637323</v>
+        <v>-4.245818122154598</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.114324906661216</v>
+        <v>1.112341473254306</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2777211127836592</v>
+        <v>-0.282679696300933</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.644392478759698</v>
+        <v>2.641417328649333</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.242042623288384</v>
+        <v>-4.24700120680566</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.105627448245317</v>
+        <v>1.103644014838407</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2833641612501707</v>
+        <v>-0.2883227447674446</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.632782425124316</v>
+        <v>2.629807275013952</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.118914916294301</v>
+        <v>-4.123873499811577</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.155430404076052</v>
+        <v>1.153446970669142</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2833641612501707</v>
+        <v>-0.2883227447674446</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.633334298157417</v>
+        <v>2.630359148047053</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.026104434843441</v>
+        <v>-4.031063018360717</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.121827288547761</v>
+        <v>1.119843855140851</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1905536797993114</v>
+        <v>-0.1955122633165852</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.618293278919299</v>
+        <v>2.615318128808934</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.977541382622411</v>
+        <v>-3.982499966139687</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.143125985360774</v>
+        <v>1.141142551953864</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1419906275782812</v>
+        <v>-0.146949211095555</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.649304586176518</v>
+        <v>2.646329436066154</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.864870164386161</v>
+        <v>-3.869828747903437</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.183270181166997</v>
+        <v>1.181286747760087</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.02931940934203098</v>
+        <v>-0.03427799285930483</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.711983025629991</v>
+        <v>2.709007875519626</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.752493163203488</v>
+        <v>-3.757451746720764</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.233712277470734</v>
+        <v>1.231728844063823</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.02931940934203098</v>
+        <v>-0.03427799285930483</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.717474321460658</v>
+        <v>2.714499171350294</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.950727732090219</v>
+        <v>-3.955686315607494</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.165915651684581</v>
+        <v>1.16393221827767</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2275539782287616</v>
+        <v>-0.2325125617460354</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.610030781897159</v>
+        <v>2.607055631786794</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.033729013115497</v>
+        <v>-4.038687596632773</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9710708592751225</v>
+        <v>0.9690874258682123</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2461248627559353</v>
+        <v>-0.2510834462732092</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.437243971181508</v>
+        <v>2.434268821071143</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.874534741058921</v>
+        <v>-3.879493324576197</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.154898228816959</v>
+        <v>1.152914795410048</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2461248627559353</v>
+        <v>-0.2510834462732092</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.557393631900713</v>
+        <v>2.554418481790349</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.961133324040024</v>
+        <v>-3.9660919075573</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.134771821726841</v>
+        <v>1.13278838831993</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2461248627559353</v>
+        <v>-0.2510834462732092</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.571906658003036</v>
+        <v>2.568931507892672</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.922749661481873</v>
+        <v>-3.927708244999149</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.14754472809247</v>
+        <v>1.145561294685559</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2077412001977841</v>
+        <v>-0.212699783715058</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.592356296880296</v>
+        <v>2.589381146769932</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.745633331446707</v>
+        <v>-3.750591914963982</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.215120288951838</v>
+        <v>1.213136855544928</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2077412001977841</v>
+        <v>-0.212699783715058</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.589085325725598</v>
+        <v>2.586110175615234</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.715931207470413</v>
+        <v>-3.720889790987689</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.227684530304268</v>
+        <v>1.225701096897358</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2122113254130975</v>
+        <v>-0.2171699089303714</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.587086642358323</v>
+        <v>2.584111492247958</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.536555786231645</v>
+        <v>-3.541514369748921</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.29322167410619</v>
+        <v>1.29123824069928</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.05543456724237883</v>
+        <v>-0.06039315075965268</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.674939672567168</v>
+        <v>2.671964522456804</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.581569999752251</v>
+        <v>-3.586528583269527</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.256023444029537</v>
+        <v>1.254040010622627</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.08578346255698344</v>
+        <v>-0.09074204607425729</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.637537790709995</v>
+        <v>2.634562640599631</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.848574510024687</v>
+        <v>-3.853533093541962</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.154913202259509</v>
+        <v>1.152929768852599</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.280146500599932</v>
+        <v>-0.2851050841172059</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.526611530223172</v>
+        <v>2.523636380112808</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.137361730483602</v>
+        <v>-4.142320314000878</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.038602235972444</v>
+        <v>1.036618802565534</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3812326206989324</v>
+        <v>-0.3861912042162062</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.465163780060273</v>
+        <v>2.462188629949909</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.10488614431283</v>
+        <v>-4.109844727830105</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.04919243199507</v>
+        <v>1.04720899858816</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3812326206989324</v>
+        <v>-0.3861912042162062</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.46276374161459</v>
+        <v>2.459788591504226</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.085848016605532</v>
+        <v>-4.090806600122808</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.053332402286234</v>
+        <v>1.051348968879323</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4394162320301269</v>
+        <v>-0.4443748155474008</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.424378294024118</v>
+        <v>2.421403143913754</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.102593881861908</v>
+        <v>-4.107552465379183</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.224215925122364</v>
+        <v>1.222232491715454</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4394162320301269</v>
+        <v>-0.4443748155474008</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.601960162962799</v>
+        <v>2.598985012852435</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.154914262462699</v>
+        <v>-4.159872845979975</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.204121101868181</v>
+        <v>1.202137668461271</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4044693720212548</v>
+        <v>-0.4094279555385286</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.623761607954255</v>
+        <v>2.620786457843891</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.299237168387618</v>
+        <v>-4.304195751904894</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.152400469895139</v>
+        <v>1.150417036488229</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4044693720212548</v>
+        <v>-0.4094279555385286</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.629770138351181</v>
+        <v>2.626794988240817</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.44376840957746</v>
+        <v>3.740535128197841</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.152351868890342</v>
+        <v>-4.147354903764207</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.290307237486072</v>
+        <v>1.292306023536526</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2372329502584797</v>
+        <v>-0.2173720601909914</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.809264639200868</v>
+        <v>2.821181173241361</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240517.xlsx
+++ b/tame_output/ON/bt/strategyON_20240517.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>47.3%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.2%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.8%</t>
+          <t>111.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>129.6%</t>
+          <t>129.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>92.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.7%</t>
+          <t>-53.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.1%</t>
+          <t>-71.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>92.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.5%</t>
+          <t>-11.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-576.3%</t>
+          <t>-546.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>268.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>100.1%</t>
+          <t>98.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-247.0%</t>
+          <t>-216.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-24.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-101.8%</t>
+          <t>-97.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-245.7%</t>
+          <t>-224.6%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-163.9%</t>
+          <t>-132.5%</t>
         </is>
       </c>
     </row>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969594</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923088</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.33643685794989</v>
+        <v>-10.33147827443261</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.959311173137559</v>
+        <v>-0.9573277397306494</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.505930133470775</v>
+        <v>-2.500971549953501</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.672061914273678</v>
+        <v>1.675037064384042</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.07259999074582</v>
+        <v>-10.06764140722854</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8636599075688394</v>
+        <v>-0.8616764741619298</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.505930133470775</v>
+        <v>-2.500971549953501</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.662178432960771</v>
+        <v>1.665153583071135</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.805358189877419</v>
+        <v>-9.800399606360145</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7585977477208536</v>
+        <v>-0.7566143143139441</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.505930133470775</v>
+        <v>-2.500971549953501</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.660343872461397</v>
+        <v>1.663319022571761</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781945</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.707451151200928</v>
+        <v>-9.702492567683654</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7197352472237184</v>
+        <v>-0.7177518138168089</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.437944383610218</v>
+        <v>-2.432985800092944</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.70083500740427</v>
+        <v>1.703810157514634</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.68349761022497</v>
+        <v>-9.678539026707696</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7094853246878414</v>
+        <v>-0.7075018912809319</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.413990842634261</v>
+        <v>-2.409032259116987</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.715875638135338</v>
+        <v>1.718850788245702</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78930753648777</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.419437671902173</v>
+        <v>-9.414479088384899</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6171216655204748</v>
+        <v>-0.6151382321135652</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.149930904311465</v>
+        <v>-2.144972320794191</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.861051284967263</v>
+        <v>1.864026435077628</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309724</v>
+        <v>3.833249172309726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.712358048397336</v>
+        <v>-8.707399464880062</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3370768497788408</v>
+        <v>-0.3350934163719312</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.149930904311465</v>
+        <v>-2.144972320794191</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.858264251306962</v>
+        <v>1.861239401417327</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858727</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.672173750031146</v>
+        <v>-8.667215166513872</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3206595065445232</v>
+        <v>-0.3186760731376137</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.109746605945274</v>
+        <v>-2.104788022428</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.882718454214518</v>
+        <v>1.885693604324883</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096473</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.592103954493341</v>
+        <v>-8.587145370976067</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2892647671086443</v>
+        <v>-0.2872813337017348</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.02967681040747</v>
+        <v>-2.024718226890196</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.930127152757958</v>
+        <v>1.933102302868322</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.78732685376181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.358622732263743</v>
+        <v>-8.353664148746468</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1879478493789533</v>
+        <v>-0.1859644159720428</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.796195588177871</v>
+        <v>-1.791237004660597</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.078140314933569</v>
+        <v>2.081115465043934</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.208956341256229</v>
+        <v>-8.203997757738954</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1309735032889066</v>
+        <v>-0.1289900698819961</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.703292096935335</v>
+        <v>-1.698333513418061</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.130990199366131</v>
+        <v>2.133965349476496</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860428</v>
+        <v>3.76317867286043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.076680867625342</v>
+        <v>-8.071722284108066</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.08269582708952461</v>
+        <v>-0.08071239368261418</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.571016623304449</v>
+        <v>-1.566058039787175</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.205722970291691</v>
+        <v>2.208698120402055</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.886081192952189</v>
+        <v>-7.881122609434914</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.00364089653262667</v>
+        <v>-0.001657463125716685</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.380416948631296</v>
+        <v>-1.375458365114022</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.322897835783219</v>
+        <v>2.325872985893583</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.637081394268608</v>
+        <v>-7.632122810751333</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1088653641644641</v>
+        <v>0.1108487975713746</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.380416948631296</v>
+        <v>-1.375458365114022</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.335804177006878</v>
+        <v>2.338779327117242</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.742671384041713</v>
+        <v>-7.737712800524437</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.06134656134399608</v>
+        <v>-0.05936312793708609</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.4860069384044</v>
+        <v>-1.481048354887126</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.144474253543796</v>
+        <v>2.147449403654161</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.76140628616031</v>
+        <v>-7.756447702643034</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.02029618031434843</v>
+        <v>-0.01831274690743845</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.4860069384044</v>
+        <v>-1.481048354887126</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.193018595420883</v>
+        <v>2.195993745531247</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.61346624475271</v>
+        <v>-7.608507661235435</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.08099908643947629</v>
+        <v>-0.0790156530325663</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.465686022495843</v>
+        <v>-1.460727438978569</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.08533222227785</v>
+        <v>2.088307372388214</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879202</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.589237608363738</v>
+        <v>-7.584279024846462</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.08002161813736564</v>
+        <v>-0.07803818473045521</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.44145738610687</v>
+        <v>-1.436498802589596</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.091155417857755</v>
+        <v>2.094130567968119</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.545689201593047</v>
+        <v>-7.540730618075772</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.06956286752418261</v>
+        <v>-0.06757943411727219</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.44145738610687</v>
+        <v>-1.436498802589596</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.084194805762662</v>
+        <v>2.087169955873026</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963419</v>
+        <v>3.782918957963421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.303540808139189</v>
+        <v>-7.298582224621914</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.04175884423850373</v>
+        <v>0.04374227764541416</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.44145738610687</v>
+        <v>-1.436498802589596</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.098657160143805</v>
+        <v>2.101632310254169</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.240311436370841</v>
+        <v>-7.235352852853565</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.06158271340503818</v>
+        <v>0.06356614681194817</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.44145738610687</v>
+        <v>-1.436498802589596</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.093189280603</v>
+        <v>2.096164430713364</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.11702030155371</v>
+        <v>-7.112061718036434</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1083972613424673</v>
+        <v>0.1103806947493777</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.31816625128974</v>
+        <v>-1.313207667772466</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.164662055503855</v>
+        <v>2.167637205614219</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389911</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.095871102650267</v>
+        <v>-7.090912519132991</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1245579191411696</v>
+        <v>0.1265413525480801</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.297017052386296</v>
+        <v>-1.292058468869023</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.185052553083247</v>
+        <v>2.188027703193611</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788094</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.852105660666822</v>
+        <v>-6.847147077149547</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2178448042815981</v>
+        <v>0.2198282376885086</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.297017052386296</v>
+        <v>-1.292058468869023</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.180833261430297</v>
+        <v>2.183808411540661</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.705208632948953</v>
+        <v>-6.700250049431677</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2787279292887623</v>
+        <v>0.2807113626956723</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.249358810407708</v>
+        <v>-1.244400226890435</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.211552520537466</v>
+        <v>2.21452767064783</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.826351398749185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.455358238999878</v>
+        <v>-6.450399655482602</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.371410161852094</v>
+        <v>0.3733935952590044</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.249358810407708</v>
+        <v>-1.244400226890435</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.204294595521168</v>
+        <v>2.207269745631532</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.279466146532446</v>
+        <v>-6.27450756301517</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4453661223597156</v>
+        <v>0.4473495557666261</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.249358810407708</v>
+        <v>-1.244400226890435</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.207893719041817</v>
+        <v>2.210868869152181</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.780930335862988</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.108019683509982</v>
+        <v>-6.103061099992707</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5272722136232546</v>
+        <v>0.529255647030165</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.077912347385245</v>
+        <v>-1.072953763867972</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.324089102909848</v>
+        <v>2.327064253020212</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.88298668384116</v>
+        <v>-5.878028100323884</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6163058911070811</v>
+        <v>0.6182893245139911</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8528793477164226</v>
+        <v>-0.8479207641991487</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.458129380327439</v>
+        <v>2.461104530437803</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.764614304353074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.819350941607225</v>
+        <v>-5.814392358089949</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.646454989054972</v>
+        <v>0.6484384224618824</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7892436054824881</v>
+        <v>-0.7842850219652142</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.501005626722117</v>
+        <v>2.503980776832481</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.798811195544783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.726350900401327</v>
+        <v>-5.721392316884051</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.664849264321127</v>
+        <v>0.6668326977280374</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7892436054824881</v>
+        <v>-0.7842850219652142</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.482199885505913</v>
+        <v>2.485175035616277</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.797691308712294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.485920403596467</v>
+        <v>-5.480961820079191</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7627645396679483</v>
+        <v>0.7647479730748588</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5488131086776278</v>
+        <v>-0.5438545251603539</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.628201260213706</v>
+        <v>2.63117641032407</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837684</v>
+        <v>3.821589933837686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.413677835425272</v>
+        <v>-5.408719251907996</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7955908807712464</v>
+        <v>0.7975743141781568</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5488131086776278</v>
+        <v>-0.5438545251603539</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.632130574048526</v>
+        <v>2.63510572415889</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349966</v>
+        <v>3.822323422349967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.297737985800087</v>
+        <v>-5.292779402282811</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8426454045386609</v>
+        <v>0.8446288379455709</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.4719913776615039</v>
+        <v>-0.46703279414423</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.678902196575541</v>
+        <v>2.681877346685905</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861305097234</v>
+        <v>3.848613050972341</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.055082397376923</v>
+        <v>-5.050123813859647</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9367057111279196</v>
+        <v>0.93868914453483</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.4719913776615039</v>
+        <v>-0.46703279414423</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.675900267795534</v>
+        <v>2.678875417905898</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.81866537614594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.835061599339912</v>
+        <v>-4.830103015822637</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.026293067353338</v>
+        <v>1.028276500760248</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3307715325935237</v>
+        <v>-0.3258129490762498</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.762211211846936</v>
+        <v>2.7651863619573</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327095200995</v>
+        <v>3.843270952009952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.702193910276635</v>
+        <v>-4.697235326759359</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.095334325780472</v>
+        <v>1.097317759187383</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3307715325935237</v>
+        <v>-0.3258129490762498</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.778105394648759</v>
+        <v>2.781080544759124</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966258</v>
+        <v>3.84504381096626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.542678806757265</v>
+        <v>-4.537720223239989</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.160286211628522</v>
+        <v>1.162269645035432</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1712564290741537</v>
+        <v>-0.1662978455568799</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.874960301200683</v>
+        <v>2.877935451311048</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046996</v>
+        <v>3.791269976046998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.398006661657528</v>
+        <v>-4.393048078140252</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.228243172229857</v>
+        <v>1.230226605636767</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.02658428397441631</v>
+        <v>-0.02162570045714246</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.971851690821966</v>
+        <v>2.97482684093233</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412104</v>
+        <v>3.735835647412106</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.45788148901522</v>
+        <v>-4.452922905497944</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.190330732688206</v>
+        <v>1.192314166095116</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.08645911133210843</v>
+        <v>-0.08150052781483458</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.921964285808776</v>
+        <v>2.924939435919141</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144515</v>
+        <v>3.762643902144517</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.371081991236212</v>
+        <v>-4.366123407718936</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.247451025122375</v>
+        <v>1.249434458529286</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.08645911133210843</v>
+        <v>-0.08150052781483458</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.944364779131342</v>
+        <v>2.947339929241707</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900693</v>
+        <v>3.729142822900695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.373551697698018</v>
+        <v>-4.368593114180742</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.246535543911065</v>
+        <v>1.248518977317975</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.08892881779391459</v>
+        <v>-0.08397023427664074</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.942955356627671</v>
+        <v>2.945930506738035</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432166204736</v>
+        <v>3.743216620473602</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.441921884022028</v>
+        <v>-4.436963300504752</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.230194391856163</v>
+        <v>1.232177825263073</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.07965311875769965</v>
+        <v>-0.0746945352404258</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.959527698524102</v>
+        <v>2.962502848634466</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978369</v>
+        <v>3.714175563978371</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.320505454395551</v>
+        <v>-4.315546870878276</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.269197672338645</v>
+        <v>1.271181105745555</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.07965311875769965</v>
+        <v>-0.0746945352404258</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.949964407155993</v>
+        <v>2.952939557266357</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887702</v>
+        <v>3.710903155887704</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.822465843450999</v>
+        <v>3.009893804368315</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.351498613724257</v>
+        <v>-4.280544418795873</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.08150997364755</v>
+        <v>1.297319612536219</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.07965311875769965</v>
+        <v>-0.0746945352404258</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.77467397219638</v>
+        <v>2.96507708322406</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.7460389506759</v>
+        <v>3.746038950675902</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.827033075442787</v>
+        <v>3.014461036360103</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.176024353931787</v>
+        <v>-4.105070159003404</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.156266909556325</v>
+        <v>1.372076548444994</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.07965311875769965</v>
+        <v>-0.0746945352404258</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.779241204188168</v>
+        <v>2.969644315215847</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695446</v>
+        <v>3.765020747695448</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.802775104203994</v>
+        <v>2.99020306512131</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.286960606573036</v>
+        <v>-4.216006411644653</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.087634437261033</v>
+        <v>1.303444076149701</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.07965311875769965</v>
+        <v>-0.0746945352404258</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.754983232949375</v>
+        <v>2.945386343977054</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581291</v>
+        <v>3.773206721581293</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.8059064894239</v>
+        <v>2.993334450341215</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.489987184116269</v>
+        <v>-4.419032989187886</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.009555191463645</v>
+        <v>1.225364830352314</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.282679696300933</v>
+        <v>-0.2777211127836592</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.63629867164334</v>
+        <v>2.82670178267102</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734161</v>
+        <v>3.784340376734162</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.816078875856032</v>
+        <v>3.003506836773348</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.332061585180976</v>
+        <v>-4.261107390252593</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.082897817469894</v>
+        <v>1.298707456358563</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.282679696300933</v>
+        <v>-0.2777211127836592</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.646471058075472</v>
+        <v>2.836874169103153</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212297</v>
+        <v>3.786946382212299</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.811025146429893</v>
+        <v>2.998453107347208</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.245818122154598</v>
+        <v>-4.174863927226215</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.112341473254306</v>
+        <v>1.328151112142975</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.282679696300933</v>
+        <v>-0.2777211127836592</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.641417328649333</v>
+        <v>2.831820439677013</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786044</v>
+        <v>3.752023923786046</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.802800921874418</v>
+        <v>2.990228882791734</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.24700120680566</v>
+        <v>-4.176047011877277</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.103644014838407</v>
+        <v>1.319453653727076</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2883227447674446</v>
+        <v>-0.2833641612501707</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.629807275013952</v>
+        <v>2.820210386041631</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273191</v>
+        <v>3.753567590273192</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.80335279490752</v>
+        <v>2.990780755824835</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.123873499811577</v>
+        <v>-4.052919304883194</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.153446970669142</v>
+        <v>1.36925660955781</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2883227447674446</v>
+        <v>-0.2833641612501707</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.630359148047053</v>
+        <v>2.820762259074733</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333870252795</v>
+        <v>3.733387025279502</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.732625486798885</v>
+        <v>2.920053447716201</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.031063018360717</v>
+        <v>-3.960108823432334</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.119843855140851</v>
+        <v>1.33565349402952</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1955122633165852</v>
+        <v>-0.1905536797993114</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.615318128808934</v>
+        <v>2.805721239836614</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030427</v>
+        <v>3.748282241030429</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.734498962723486</v>
+        <v>2.921926923640802</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.982499966139687</v>
+        <v>-3.911545771211304</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.141142551953864</v>
+        <v>1.356952190842533</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.146949211095555</v>
+        <v>-0.1419906275782812</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.646329436066154</v>
+        <v>2.836732547093833</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942739</v>
+        <v>3.721073619942741</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.729574671235209</v>
+        <v>2.917002632152525</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.869828747903437</v>
+        <v>-3.798874552975054</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.181286747760087</v>
+        <v>1.397096386648756</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.03427799285930483</v>
+        <v>-0.02931940934203098</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.709007875519626</v>
+        <v>2.899410986547306</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268537</v>
+        <v>3.743044028268539</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.735065967065876</v>
+        <v>2.922493927983192</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.757451746720764</v>
+        <v>-3.686497551792381</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.231728844063823</v>
+        <v>1.447538482952492</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.03427799285930483</v>
+        <v>-0.02931940934203098</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.714499171350294</v>
+        <v>2.904902282377973</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968862</v>
+        <v>3.689594264968864</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.746563168834415</v>
+        <v>2.933991129751731</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.955686315607494</v>
+        <v>-3.884732120679112</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.16393221827767</v>
+        <v>1.379741857166339</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2325125617460354</v>
+        <v>-0.2275539782287616</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.607055631786794</v>
+        <v>2.797458742814474</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175322</v>
+        <v>3.643066046175324</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.584918888835069</v>
+        <v>2.772346849752384</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.038687596632773</v>
+        <v>-3.967733401704391</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9690874258682123</v>
+        <v>1.184897064756881</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2510834462732092</v>
+        <v>-0.2461248627559353</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.434268821071143</v>
+        <v>2.624671932098823</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199269</v>
+        <v>3.682712735199271</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.705068549554274</v>
+        <v>2.89249651047159</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.879493324576197</v>
+        <v>-3.808539129647814</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.152914795410048</v>
+        <v>1.368724434298717</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2510834462732092</v>
+        <v>-0.2461248627559353</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.554418481790349</v>
+        <v>2.744821592818029</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660768</v>
+        <v>3.733008865660771</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.719581575656597</v>
+        <v>2.907009536573913</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.9660919075573</v>
+        <v>-3.895137712628917</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.13278838831993</v>
+        <v>1.348598027208599</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2510834462732092</v>
+        <v>-0.2461248627559353</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.568931507892672</v>
+        <v>2.759334618920352</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383423</v>
+        <v>3.741170494383426</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.717001016998966</v>
+        <v>2.904428977916282</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.927708244999149</v>
+        <v>-3.856754050070766</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.145561294685559</v>
+        <v>1.361370933574228</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.212699783715058</v>
+        <v>-0.2077412001977841</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.589381146769932</v>
+        <v>2.779784257797612</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002484</v>
+        <v>3.751143622002487</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.713730045844268</v>
+        <v>2.901158006761584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.750591914963982</v>
+        <v>-3.6796377200356</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.213136855544928</v>
+        <v>1.428946494433597</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.212699783715058</v>
+        <v>-0.2077412001977841</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.586110175615234</v>
+        <v>2.776513286642914</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263902</v>
+        <v>3.741324873263904</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.714413437606181</v>
+        <v>2.901841398523497</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.720889790987689</v>
+        <v>-3.649935596059307</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.225701096897358</v>
+        <v>1.441510735786027</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2171699089303714</v>
+        <v>-0.2122113254130975</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.584111492247958</v>
+        <v>2.774514603275639</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481235</v>
+        <v>3.750725801481238</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.708200412912595</v>
+        <v>2.895628373829911</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.541514369748921</v>
+        <v>-3.470560174820538</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.29123824069928</v>
+        <v>1.507047879587949</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.06039315075965268</v>
+        <v>-0.05543456724237883</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.671964522456804</v>
+        <v>2.862367633484484</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71698814345223</v>
+        <v>3.716988143452233</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.689007868244185</v>
+        <v>2.876435829161501</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.586528583269527</v>
+        <v>-3.515574388341145</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.254040010622627</v>
+        <v>1.469849649511296</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.09074204607425729</v>
+        <v>-0.08578346255698344</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.634562640599631</v>
+        <v>2.824965751627311</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979538</v>
+        <v>3.73702303297954</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.694699430583131</v>
+        <v>2.882127391500447</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.853533093541962</v>
+        <v>-3.78257889861358</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.152929768852599</v>
+        <v>1.368739407741268</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2851050841172059</v>
+        <v>-0.280146500599932</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.523636380112808</v>
+        <v>2.714039491140488</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230808</v>
+        <v>3.70230587923081</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.693903352479632</v>
+        <v>2.881331313396948</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.142320314000878</v>
+        <v>-4.071366119072495</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.036618802565534</v>
+        <v>1.252428441454203</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3861912042162062</v>
+        <v>-0.3812326206989324</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.462188629949909</v>
+        <v>2.652591740977589</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285454</v>
+        <v>3.705568086285456</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.691503314033949</v>
+        <v>2.878931274951265</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.109844727830105</v>
+        <v>-4.038890532901723</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.04720899858816</v>
+        <v>1.263018637476828</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3861912042162062</v>
+        <v>-0.3812326206989324</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.459788591504226</v>
+        <v>2.650191702531906</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848102</v>
+        <v>3.709506867848104</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.688028033242194</v>
+        <v>2.87545599415951</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.090806600122808</v>
+        <v>-4.019852405194426</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.051348968879323</v>
+        <v>1.267158607767992</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4443748155474008</v>
+        <v>-0.4394162320301269</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.421403143913754</v>
+        <v>2.611806254941434</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601251</v>
+        <v>3.731060897601253</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.865609902180875</v>
+        <v>3.05303786309819</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.107552465379183</v>
+        <v>-4.036598270450801</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.222232491715454</v>
+        <v>1.438042130604123</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4443748155474008</v>
+        <v>-0.4394162320301269</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.598985012852435</v>
+        <v>2.789388123880115</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537863</v>
+        <v>3.722443786537865</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.866443231167008</v>
+        <v>3.053871192084324</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.159872845979975</v>
+        <v>-4.088918651051593</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.202137668461271</v>
+        <v>1.41794730734994</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4094279555385286</v>
+        <v>-0.4044693720212548</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.620786457843891</v>
+        <v>2.811189568871571</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259122</v>
+        <v>3.787422005259124</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.872451761563934</v>
+        <v>3.05987972248125</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.304195751904894</v>
+        <v>-4.233241556976512</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.150417036488229</v>
+        <v>1.366226675376898</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4094279555385286</v>
+        <v>-0.4044693720212548</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.626794988240817</v>
+        <v>2.817198099268497</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.740535128197841</v>
+        <v>3.75329746275926</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.951604409355956</v>
+        <v>3.139032370273272</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.147354903764207</v>
+        <v>-3.850206243280217</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.292306023536526</v>
+        <v>1.598593448647438</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2173720601909914</v>
+        <v>-0.005938710578432205</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.821181173241361</v>
+        <v>3.135469143926213</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240517.xlsx
+++ b/tame_output/ON/bt/strategyON_20240517.xlsx
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>-16.5%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-76.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.8%</t>
+          <t>110.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.8%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-53.0%</t>
+          <t>-51.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.8%</t>
+          <t>-72.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.7%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.1%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-546.6%</t>
+          <t>-569.9%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>268.9%</t>
+          <t>268.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-216.4%</t>
+          <t>-244.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.1%</t>
+          <t>-26.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-30.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-20.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-97.7%</t>
+          <t>-93.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-224.6%</t>
+          <t>-247.7%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-132.5%</t>
+          <t>-165.1%</t>
         </is>
       </c>
     </row>
@@ -46122,19 +46122,19 @@
         <v>3.710903155887704</v>
       </c>
       <c r="C1938" t="n">
-        <v>3.009893804368315</v>
+        <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.280544418795873</v>
+        <v>-4.278578690193474</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.297319612536219</v>
+        <v>1.110677943059863</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.0746945352404258</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.96507708322406</v>
+        <v>2.777649122306744</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746038950675902</v>
       </c>
       <c r="C1939" t="n">
-        <v>3.014461036360103</v>
+        <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.105070159003404</v>
+        <v>-4.103104430401006</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.372076548444994</v>
+        <v>1.185434878968638</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.0746945352404258</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.969644315215847</v>
+        <v>2.782216354298532</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765020747695448</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.99020306512131</v>
+        <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.216006411644653</v>
+        <v>-4.214040683042255</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.303444076149701</v>
+        <v>1.116802406673345</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.0746945352404258</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.945386343977054</v>
+        <v>2.757958383059739</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773206721581293</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.993334450341215</v>
+        <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.419032989187886</v>
+        <v>-4.417067260585488</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.225364830352314</v>
+        <v>1.038723160875958</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.2777211127836592</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.82670178267102</v>
+        <v>2.639273821753704</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784340376734162</v>
       </c>
       <c r="C1942" t="n">
-        <v>3.003506836773348</v>
+        <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.261107390252593</v>
+        <v>-4.259141661650195</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.298707456358563</v>
+        <v>1.112065786882207</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.2777211127836592</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.836874169103153</v>
+        <v>2.649446208185837</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786946382212299</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.998453107347208</v>
+        <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.174863927226215</v>
+        <v>-4.172898198623817</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.328151112142975</v>
+        <v>1.141509442666619</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.2777211127836592</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.831820439677013</v>
+        <v>2.644392478759698</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752023923786046</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.990228882791734</v>
+        <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.176047011877277</v>
+        <v>-4.174081283274878</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.319453653727076</v>
+        <v>1.132811984250719</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.2833641612501707</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.820210386041631</v>
+        <v>2.632782425124316</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753567590273192</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.990780755824835</v>
+        <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.052919304883194</v>
+        <v>-4.050953576280795</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.36925660955781</v>
+        <v>1.182614940081454</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.2833641612501707</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.820762259074733</v>
+        <v>2.633334298157417</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733387025279502</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.920053447716201</v>
+        <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.960108823432334</v>
+        <v>-3.958143094829936</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.33565349402952</v>
+        <v>1.149011824553164</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.1905536797993114</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.805721239836614</v>
+        <v>2.618293278919299</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748282241030429</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.921926923640802</v>
+        <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.911545771211304</v>
+        <v>-3.909580042608906</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.356952190842533</v>
+        <v>1.170310521366177</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.1419906275782812</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.836732547093833</v>
+        <v>2.649304586176518</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721073619942741</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.917002632152525</v>
+        <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.798874552975054</v>
+        <v>-3.796908824372656</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.397096386648756</v>
+        <v>1.2104547171724</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.02931940934203098</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.899410986547306</v>
+        <v>2.711983025629991</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743044028268539</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.922493927983192</v>
+        <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.686497551792381</v>
+        <v>-3.684531823189983</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.447538482952492</v>
+        <v>1.260896813476136</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.02931940934203098</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.904902282377973</v>
+        <v>2.717474321460658</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689594264968864</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.933991129751731</v>
+        <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.884732120679112</v>
+        <v>-3.882766392076713</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.379741857166339</v>
+        <v>1.193100187689983</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2275539782287616</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.797458742814474</v>
+        <v>2.610030781897159</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643066046175324</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.772346849752384</v>
+        <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.967733401704391</v>
+        <v>-3.965767673101992</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.184897064756881</v>
+        <v>0.9982553952805244</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2461248627559353</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.624671932098823</v>
+        <v>2.437243971181508</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682712735199271</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.89249651047159</v>
+        <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.808539129647814</v>
+        <v>-3.806573401045416</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.368724434298717</v>
+        <v>1.182082764822361</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2461248627559353</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.744821592818029</v>
+        <v>2.557393631900713</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733008865660771</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.907009536573913</v>
+        <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.895137712628917</v>
+        <v>-3.893171984026519</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.348598027208599</v>
+        <v>1.161956357732242</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2461248627559353</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.759334618920352</v>
+        <v>2.571906658003036</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741170494383426</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.904428977916282</v>
+        <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.856754050070766</v>
+        <v>-3.854788321468368</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.361370933574228</v>
+        <v>1.174729264097871</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2077412001977841</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.779784257797612</v>
+        <v>2.592356296880296</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751143622002487</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.901158006761584</v>
+        <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.6796377200356</v>
+        <v>-3.677671991433202</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.428946494433597</v>
+        <v>1.24230482495724</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2077412001977841</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.776513286642914</v>
+        <v>2.589085325725598</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741324873263904</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.901841398523497</v>
+        <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.649935596059307</v>
+        <v>-3.647969867456908</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.441510735786027</v>
+        <v>1.25486906630967</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.2122113254130975</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.774514603275639</v>
+        <v>2.587086642358323</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750725801481238</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.895628373829911</v>
+        <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.470560174820538</v>
+        <v>-3.46859444621814</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.507047879587949</v>
+        <v>1.320406210111592</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.05543456724237883</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.862367633484484</v>
+        <v>2.674939672567168</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716988143452233</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.876435829161501</v>
+        <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.515574388341145</v>
+        <v>-3.513608659738746</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.469849649511296</v>
+        <v>1.283207980034939</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.08578346255698344</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.824965751627311</v>
+        <v>2.637537790709995</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.73702303297954</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.882127391500447</v>
+        <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.78257889861358</v>
+        <v>-3.780613170011182</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.368739407741268</v>
+        <v>1.182097738264911</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.280146500599932</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.714039491140488</v>
+        <v>2.526611530223172</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.70230587923081</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.881331313396948</v>
+        <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.071366119072495</v>
+        <v>-4.069400390470097</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.252428441454203</v>
+        <v>1.065786771977846</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.3812326206989324</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.652591740977589</v>
+        <v>2.465163780060273</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705568086285456</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.878931274951265</v>
+        <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.038890532901723</v>
+        <v>-4.036924804299325</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.263018637476828</v>
+        <v>1.076376968000472</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.3812326206989324</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.650191702531906</v>
+        <v>2.46276374161459</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709506867848104</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.87545599415951</v>
+        <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.019852405194426</v>
+        <v>-4.017886676592028</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.267158607767992</v>
+        <v>1.080516938291636</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4394162320301269</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.611806254941434</v>
+        <v>2.424378294024118</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731060897601253</v>
       </c>
       <c r="C1963" t="n">
-        <v>3.05303786309819</v>
+        <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.036598270450801</v>
+        <v>-4.034632541848403</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.438042130604123</v>
+        <v>1.251400461127766</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4394162320301269</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.789388123880115</v>
+        <v>2.601960162962799</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722443786537865</v>
       </c>
       <c r="C1964" t="n">
-        <v>3.053871192084324</v>
+        <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.088918651051593</v>
+        <v>-4.086952922449195</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.41794730734994</v>
+        <v>1.231305637873583</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.4044693720212548</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.811189568871571</v>
+        <v>2.623761607954255</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787422005259124</v>
       </c>
       <c r="C1965" t="n">
-        <v>3.05987972248125</v>
+        <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.233241556976512</v>
+        <v>-4.231275828374113</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.366226675376898</v>
+        <v>1.179585005900541</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.4044693720212548</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.817198099268497</v>
+        <v>2.629770138351181</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.75329746275926</v>
       </c>
       <c r="C1966" t="n">
-        <v>3.139032370273272</v>
+        <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.850206243280217</v>
+        <v>-4.083532858139111</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.598593448647438</v>
+        <v>1.317834841786564</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.005938710578432205</v>
+        <v>-0.2366620147863716</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.135469143926213</v>
+        <v>2.809607200484133</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240517.xlsx
+++ b/tame_output/ON/bt/strategyON_20240517.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-8.4%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.8%</t>
+          <t>110.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>129.7%</t>
+          <t>129.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.2%</t>
+          <t>-20.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-165.1%</t>
+          <t>-143.5%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1966"/>
+  <dimension ref="A1:G1967"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309726</v>
+        <v>3.833249172309724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.839370871858727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78732685376181</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255787</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76317867286043</v>
+        <v>3.763178672860428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575955</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430989</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879202</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568109</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963421</v>
+        <v>3.782918957963419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192819</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262049</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389911</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788096</v>
+        <v>3.748324832788094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527527</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749185</v>
+        <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481497</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862988</v>
+        <v>3.780930335862986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353074</v>
+        <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544783</v>
+        <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712294</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837686</v>
+        <v>3.821589933837684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349967</v>
+        <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972341</v>
+        <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866537614594</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009952</v>
+        <v>3.84327095200995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504381096626</v>
+        <v>3.845043810966258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046998</v>
+        <v>3.791269976046996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412106</v>
+        <v>3.735835647412104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144517</v>
+        <v>3.762643902144515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900695</v>
+        <v>3.729142822900693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473602</v>
+        <v>3.7432166204736</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978371</v>
+        <v>3.714175563978369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887704</v>
+        <v>3.710903155887702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675902</v>
+        <v>3.7460389506759</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695448</v>
+        <v>3.765020747695446</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581293</v>
+        <v>3.773206721581291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734162</v>
+        <v>3.784340376734161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212299</v>
+        <v>3.786946382212297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786046</v>
+        <v>3.752023923786044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273192</v>
+        <v>3.753567590273191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279502</v>
+        <v>3.7333870252795</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030429</v>
+        <v>3.748282241030427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942741</v>
+        <v>3.721073619942739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268539</v>
+        <v>3.743044028268537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968864</v>
+        <v>3.689594264968862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175324</v>
+        <v>3.643066046175322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199271</v>
+        <v>3.682712735199269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660771</v>
+        <v>3.733008865660769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383426</v>
+        <v>3.741170494383423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002487</v>
+        <v>3.751143622002484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263904</v>
+        <v>3.741324873263903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481238</v>
+        <v>3.750725801481236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452233</v>
+        <v>3.716988143452231</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702303297954</v>
+        <v>3.737023032979538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230587923081</v>
+        <v>3.702305879230808</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285456</v>
+        <v>3.705568086285454</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848104</v>
+        <v>3.709506867848102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601253</v>
+        <v>3.731060897601251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537865</v>
+        <v>3.722443786537863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259124</v>
+        <v>3.787422005259122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.75329746275926</v>
+        <v>3.781497674989909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
@@ -46779,6 +46779,29 @@
       </c>
       <c r="G1966" t="n">
         <v>2.809607200484133</v>
+      </c>
+    </row>
+    <row r="1967">
+      <c r="A1967" s="2" t="n">
+        <v>45429</v>
+      </c>
+      <c r="B1967" t="n">
+        <v>3.753129399727435</v>
+      </c>
+      <c r="C1967" t="n">
+        <v>3.032647997152236</v>
+      </c>
+      <c r="D1967" t="n">
+        <v>-4.083532858139111</v>
+      </c>
+      <c r="E1967" t="n">
+        <v>1.317834841786564</v>
+      </c>
+      <c r="F1967" t="n">
+        <v>-0.2366620147863716</v>
+      </c>
+      <c r="G1967" t="n">
+        <v>3.025711794138604</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240517.xlsx
+++ b/tame_output/ON/bt/strategyON_20240517.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.9%</t>
+          <t>-77.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>129.6%</t>
+          <t>129.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.8%</t>
+          <t>-73.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-10.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-569.9%</t>
+          <t>-576.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-244.4%</t>
+          <t>-247.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-143.5%</t>
+          <t>-152.0%</t>
         </is>
       </c>
     </row>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.721392316884051</v>
+        <v>-5.718907369837223</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6668326977280374</v>
+        <v>0.6678266765467686</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.7842850219652142</v>
@@ -45826,10 +45826,10 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.480961820079191</v>
+        <v>-5.478476873032363</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7647479730748588</v>
+        <v>0.76574195189359</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.5438545251603539</v>
@@ -45849,10 +45849,10 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.408719251907996</v>
+        <v>-5.406234304861168</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7975743141781568</v>
+        <v>0.798568292996888</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5438545251603539</v>
@@ -45872,10 +45872,10 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.292779402282811</v>
+        <v>-5.290294455235983</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8446288379455709</v>
+        <v>0.8456228167643025</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.46703279414423</v>
@@ -45895,10 +45895,10 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.050123813859647</v>
+        <v>-5.04763886681282</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.93868914453483</v>
+        <v>0.9396831233535607</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.46703279414423</v>
@@ -45918,10 +45918,10 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.830103015822637</v>
+        <v>-4.827618068775809</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.028276500760248</v>
+        <v>1.029270479578979</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.3258129490762498</v>
@@ -45941,10 +45941,10 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.697235326759359</v>
+        <v>-4.694750379712532</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.097317759187383</v>
+        <v>1.098311738006114</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.3258129490762498</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.537720223239989</v>
+        <v>-4.535235276193162</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.162269645035432</v>
+        <v>1.163263623854163</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.1662978455568799</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.393048078140252</v>
+        <v>-4.390563131093424</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.230226605636767</v>
+        <v>1.231220584455498</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.02162570045714246</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.452922905497944</v>
+        <v>-4.450437958451117</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.192314166095116</v>
+        <v>1.193308144913847</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.08150052781483458</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.366123407718936</v>
+        <v>-4.363638460672108</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.249434458529286</v>
+        <v>1.250428437348017</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.08150052781483458</v>
@@ -46056,10 +46056,10 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.368593114180742</v>
+        <v>-4.366108167133914</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.248518977317975</v>
+        <v>1.249512956136706</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.08397023427664074</v>
@@ -46079,10 +46079,10 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.436963300504752</v>
+        <v>-4.434478353457925</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.232177825263073</v>
+        <v>1.233171804081804</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.0746945352404258</v>
@@ -46102,10 +46102,10 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.315546870878276</v>
+        <v>-4.313061923831448</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.271181105745555</v>
+        <v>1.272175084564286</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.0746945352404258</v>
@@ -46125,10 +46125,10 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.278578690193474</v>
+        <v>-4.344055083160153</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.110677943059863</v>
+        <v>1.084487385873191</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.0746945352404258</v>
@@ -46148,10 +46148,10 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.103104430401006</v>
+        <v>-4.168580823367684</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.185434878968638</v>
+        <v>1.159244321781967</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.0746945352404258</v>
@@ -46171,10 +46171,10 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.214040683042255</v>
+        <v>-4.279517076008933</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.116802406673345</v>
+        <v>1.090611849486674</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.0746945352404258</v>
@@ -46194,10 +46194,10 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.417067260585488</v>
+        <v>-4.482543653552166</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.038723160875958</v>
+        <v>1.012532603689286</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.2777211127836592</v>
@@ -46217,10 +46217,10 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.259141661650195</v>
+        <v>-4.324618054616873</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.112065786882207</v>
+        <v>1.085875229695536</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.2777211127836592</v>
@@ -46240,10 +46240,10 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.172898198623817</v>
+        <v>-4.238374591590495</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.141509442666619</v>
+        <v>1.115318885479947</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.2777211127836592</v>
@@ -46263,10 +46263,10 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.174081283274878</v>
+        <v>-4.239557676241557</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.132811984250719</v>
+        <v>1.106621427064048</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.2833641612501707</v>
@@ -46286,10 +46286,10 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.050953576280795</v>
+        <v>-4.116429969247474</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.182614940081454</v>
+        <v>1.156424382894783</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.2833641612501707</v>
@@ -46309,10 +46309,10 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.958143094829936</v>
+        <v>-4.023619487796614</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.149011824553164</v>
+        <v>1.122821267366493</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.1905536797993114</v>
@@ -46332,10 +46332,10 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.909580042608906</v>
+        <v>-3.975056435575584</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.170310521366177</v>
+        <v>1.144119964179505</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.1419906275782812</v>
@@ -46355,10 +46355,10 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.796908824372656</v>
+        <v>-3.862385217339333</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.2104547171724</v>
+        <v>1.184264159985728</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.02931940934203098</v>
@@ -46378,10 +46378,10 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.684531823189983</v>
+        <v>-3.750008216156661</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.260896813476136</v>
+        <v>1.234706256289465</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.02931940934203098</v>
@@ -46401,10 +46401,10 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.882766392076713</v>
+        <v>-3.948242785043391</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.193100187689983</v>
+        <v>1.166909630503312</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2275539782287616</v>
@@ -46424,10 +46424,10 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.965767673101992</v>
+        <v>-4.03124406606867</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9982553952805244</v>
+        <v>0.9720648380938535</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2461248627559353</v>
@@ -46447,10 +46447,10 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.806573401045416</v>
+        <v>-3.872049794012093</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.182082764822361</v>
+        <v>1.15589220763569</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2461248627559353</v>
@@ -46470,10 +46470,10 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.893171984026519</v>
+        <v>-3.958648376993196</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.161956357732242</v>
+        <v>1.135765800545572</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2461248627559353</v>
@@ -46493,10 +46493,10 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.854788321468368</v>
+        <v>-3.920264714435045</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.174729264097871</v>
+        <v>1.148538706911201</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2077412001977841</v>
@@ -46516,10 +46516,10 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.677671991433202</v>
+        <v>-3.743148384399879</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.24230482495724</v>
+        <v>1.216114267770569</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2077412001977841</v>
@@ -46539,10 +46539,10 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.647969867456908</v>
+        <v>-3.713446260423586</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.25486906630967</v>
+        <v>1.228678509122999</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.2122113254130975</v>
@@ -46562,10 +46562,10 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.46859444621814</v>
+        <v>-3.534070839184817</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.320406210111592</v>
+        <v>1.294215652924921</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.05543456724237883</v>
@@ -46585,10 +46585,10 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.513608659738746</v>
+        <v>-3.579085052705424</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.283207980034939</v>
+        <v>1.257017422848268</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.08578346255698344</v>
@@ -46608,10 +46608,10 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.780613170011182</v>
+        <v>-3.846089562977859</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.182097738264911</v>
+        <v>1.15590718107824</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.280146500599932</v>
@@ -46631,10 +46631,10 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.069400390470097</v>
+        <v>-4.134876783436774</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.065786771977846</v>
+        <v>1.039596214791175</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.3812326206989324</v>
@@ -46654,10 +46654,10 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.036924804299325</v>
+        <v>-4.102401197266002</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.076376968000472</v>
+        <v>1.050186410813801</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.3812326206989324</v>
@@ -46677,10 +46677,10 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.017886676592028</v>
+        <v>-4.083363069558705</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.080516938291636</v>
+        <v>1.054326381104965</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4394162320301269</v>
@@ -46700,10 +46700,10 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.034632541848403</v>
+        <v>-4.10010893481508</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.251400461127766</v>
+        <v>1.225209903941095</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4394162320301269</v>
@@ -46723,10 +46723,10 @@
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.086952922449195</v>
+        <v>-4.152429315415872</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.231305637873583</v>
+        <v>1.205115080686912</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.4044693720212548</v>
@@ -46746,10 +46746,10 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.231275828374113</v>
+        <v>-4.296752221340791</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.179585005900541</v>
+        <v>1.153394448713871</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.4044693720212548</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989909</v>
+        <v>3.781497674989907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.083532858139111</v>
+        <v>-4.149009251105788</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.317834841786564</v>
+        <v>1.291644284599893</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.2366620147863716</v>
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.753129399727435</v>
+        <v>3.755691284366996</v>
       </c>
       <c r="C1967" t="n">
-        <v>3.032647997152236</v>
+        <v>2.947296864113548</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.083532858139111</v>
+        <v>-4.149009251105788</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.317834841786564</v>
+        <v>1.291644284599893</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.2366620147863716</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.025711794138604</v>
+        <v>2.940360661099916</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240517.xlsx
+++ b/tame_output/ON/bt/strategyON_20240517.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>15.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,32 +834,32 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-37.3%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.2%</t>
+          <t>-77.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.7%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>129.5%</t>
+          <t>128.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.7%</t>
+          <t>-52.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.2%</t>
+          <t>-74.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.7%</t>
+          <t>445.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.5%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-576.5%</t>
+          <t>-603.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.3%</t>
+          <t>-41.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>268.8%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>344.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-247.1%</t>
+          <t>-257.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-26.6%</t>
+          <t>-25.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.6%</t>
+          <t>-30.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.3%</t>
+          <t>-19.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-93.6%</t>
+          <t>-295.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-247.7%</t>
+          <t>-238.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-27.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-152.0%</t>
+          <t>-172.4%</t>
         </is>
       </c>
     </row>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.737481338317957</v>
+        <v>-5.635072811292202</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8220755012821512</v>
+        <v>0.8630389120924535</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.7840373989212537</v>
+        <v>-0.6896061206682944</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.647002021570329</v>
+        <v>2.703660788522105</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.102608720956703</v>
+        <v>-6.000200193930948</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6752790632324839</v>
+        <v>0.7162424740427862</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.080348183220266</v>
+        <v>-0.9859169049673069</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.468470065996753</v>
+        <v>2.525128832948529</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.511197498137381</v>
+        <v>-6.408788971111626</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.510605096374972</v>
+        <v>0.5515685071852738</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.394505682147985</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.222078343703105</v>
+        <v>2.278737110654881</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.924179982278475</v>
+        <v>-6.82177145525272</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3405975351899948</v>
+        <v>0.3815609460002971</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.394505682147985</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.217263776174566</v>
+        <v>2.273922543126341</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.340571856565473</v>
+        <v>-7.238163329539717</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1720348360840731</v>
+        <v>0.2129982468943754</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.394505682147985</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.215257826783443</v>
+        <v>2.271916593735219</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.717248867095317</v>
+        <v>-7.614840340069562</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.03162272254081433</v>
+        <v>0.07258613335111663</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.394505682147985</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.225516517452122</v>
+        <v>2.282175284403898</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.063123689080125</v>
+        <v>-7.96071516205437</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1106276411074139</v>
+        <v>-0.06966423029711155</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.394505682147985</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.221616082597818</v>
+        <v>2.278274849549593</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.22670356726451</v>
+        <v>-8.124295040238755</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1776546723261663</v>
+        <v>-0.1366912615158644</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.394505682147985</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.220021002652818</v>
+        <v>2.276679769604594</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.523364909074708</v>
+        <v>-8.420956382048953</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2925402331210374</v>
+        <v>-0.2515768223107355</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.557680096134823</v>
+        <v>-1.463248817881864</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.182554097141699</v>
+        <v>2.239212864093475</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.646609298290137</v>
+        <v>-8.544200771264382</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3458642933416125</v>
+        <v>-0.3049008825313102</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.557680096134823</v>
+        <v>-1.463248817881864</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.178527792607296</v>
+        <v>2.235186559559072</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.029610687032768</v>
+        <v>-8.927202160007013</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4991669501602489</v>
+        <v>-0.4582035393499471</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.557680096134823</v>
+        <v>-1.463248817881864</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.178425691285712</v>
+        <v>2.235084458237488</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.187009567245889</v>
+        <v>-9.084601040220134</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5595549862740672</v>
+        <v>-0.5185915754637649</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.715078976347944</v>
+        <v>-1.620647698094985</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.08655787912927</v>
+        <v>2.143216646081045</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.546539889749891</v>
+        <v>-9.444131362724136</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6980168119776176</v>
+        <v>-0.6570534011673157</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.715078976347944</v>
+        <v>-1.620647698094985</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.09190818242732</v>
+        <v>2.148566949379095</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.596888953204113</v>
+        <v>-9.494480426178358</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7102404174021291</v>
+        <v>-0.6692770065918268</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.765428039802166</v>
+        <v>-1.670996761549207</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.069614764311964</v>
+        <v>2.12627353126374</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.81603792127831</v>
+        <v>-9.713629394252555</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7948582540100388</v>
+        <v>-0.753894843199737</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.984577007876364</v>
+        <v>-1.890145729623404</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.941167134089214</v>
+        <v>1.99782590104099</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.812346996321899</v>
+        <v>-9.709938469296144</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7933818840274749</v>
+        <v>-0.7524184732171726</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.984577007876364</v>
+        <v>-1.890145729623404</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.941167134089214</v>
+        <v>1.99782590104099</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.01660517165176</v>
+        <v>-9.914196644626008</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8695719570407778</v>
+        <v>-0.828608546230476</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.112215952490353</v>
+        <v>-2.017784674237393</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.870096964439463</v>
+        <v>1.926755731391239</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.23464294328294</v>
+        <v>-10.13223441625719</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9523045112088124</v>
+        <v>-0.9113411003985106</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.286986720586252</v>
+        <v>-2.192555442333292</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.76971705806636</v>
+        <v>1.826375825018136</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.16117311161549</v>
+        <v>-10.05876458458974</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9075448770484122</v>
+        <v>-0.8665814662381104</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.213516888918803</v>
+        <v>-2.119085610665844</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.82917065856025</v>
+        <v>1.885829425512026</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.33629752900204</v>
+        <v>-10.23388900197628</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9630394232555126</v>
+        <v>-0.9220760124452108</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.388641306305347</v>
+        <v>-2.294210028052388</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.738651228875841</v>
+        <v>1.795309995827617</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.57074962301652</v>
+        <v>-10.46834109599077</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.064039425762905</v>
+        <v>-1.023076014952603</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.388641306305347</v>
+        <v>-2.294210028052388</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.731432063974245</v>
+        <v>1.788090830926021</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.85855346755376</v>
+        <v>-10.75614494052801</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.185833154351776</v>
+        <v>-1.144869743541474</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.676445150842585</v>
+        <v>-2.582013872589626</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.552077566477926</v>
+        <v>1.608736333429701</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.91133962315409</v>
+        <v>-10.80893109612833</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.20583182675335</v>
+        <v>-1.164868415943048</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.772120637424982</v>
+        <v>-2.677689359172023</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.495788064367044</v>
+        <v>1.55244683131882</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.14336854289035</v>
+        <v>-11.0409600158646</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.29594966601874</v>
+        <v>-1.254986255208439</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.834133334613405</v>
+        <v>-2.739702056360446</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.461274174683105</v>
+        <v>1.51793294163488</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.09135302892154</v>
+        <v>-10.98894450189578</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.271153124744814</v>
+        <v>-1.230189713934513</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.834133334613405</v>
+        <v>-2.739702056360446</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.465264510369505</v>
+        <v>1.521923277321281</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.23302487064566</v>
+        <v>-11.1306163436199</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.329297088333204</v>
+        <v>-1.288333677522902</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.834133334613405</v>
+        <v>-2.739702056360446</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.463789283470764</v>
+        <v>1.520448050422539</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.18343402622082</v>
+        <v>-11.08102549919507</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.294407340398398</v>
+        <v>-1.253443929588097</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.784542490188572</v>
+        <v>-2.690111211935612</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.508597200290536</v>
+        <v>1.565255967242312</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.98428191898373</v>
+        <v>-10.88187339195797</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.227797631150242</v>
+        <v>-1.18683422033994</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.619219964238758</v>
+        <v>-2.524788685985799</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.594739582213741</v>
+        <v>1.651398349165517</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.75843676626431</v>
+        <v>-10.65602823923856</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.127880497026268</v>
+        <v>-1.086917086215966</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.577293288651595</v>
+        <v>-2.482862010398635</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.629474660602248</v>
+        <v>1.686133427554024</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.63385810992672</v>
+        <v>-10.53144958290097</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.076909889935173</v>
+        <v>-1.035946479124871</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.577293288651595</v>
+        <v>-2.482862010398635</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.630613805158307</v>
+        <v>1.687272572110083</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.68675339797101</v>
+        <v>-10.58434487094525</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.095434230990779</v>
+        <v>-1.054470820180478</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.572337942563149</v>
+        <v>-2.477906664310189</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.636220786973482</v>
+        <v>1.692879553925258</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.40284466704226</v>
+        <v>-10.3004361400165</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9761370343806437</v>
+        <v>-0.9351736235703418</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.572337942563149</v>
+        <v>-2.477906664310189</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.641954491212119</v>
+        <v>1.698613258163895</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.33147827443261</v>
+        <v>-10.22906974740686</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9573277397306494</v>
+        <v>-0.9163643289203476</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.500971549953501</v>
+        <v>-2.406540271700541</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.675037064384042</v>
+        <v>1.731695831335818</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.06764140722854</v>
+        <v>-9.965232880202787</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8616764741619298</v>
+        <v>-0.8207130633516275</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.500971549953501</v>
+        <v>-2.406540271700541</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.665153583071135</v>
+        <v>1.72181235002291</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.800399606360145</v>
+        <v>-9.885298101616605</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7566143143139441</v>
+        <v>-0.7905737124165282</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.500971549953501</v>
+        <v>-2.406540271700541</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.663319022571761</v>
+        <v>1.719977789523537</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.702492567683654</v>
+        <v>-9.787391062940115</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7177518138168089</v>
+        <v>-0.7517112119193929</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.432985800092944</v>
+        <v>-2.338554521839985</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.703810157514634</v>
+        <v>1.76046892446641</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.678539026707696</v>
+        <v>-9.763437521964157</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7075018912809319</v>
+        <v>-0.741461289383516</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.409032259116987</v>
+        <v>-2.314600980864027</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.718850788245702</v>
+        <v>1.775509555197478</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.414479088384899</v>
+        <v>-9.49937758364136</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6151382321135652</v>
+        <v>-0.6490976302161497</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.144972320794191</v>
+        <v>-2.050541042541231</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.864026435077628</v>
+        <v>1.920685202029404</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.707399464880062</v>
+        <v>-8.792297960136523</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3350934163719312</v>
+        <v>-0.3690528144745153</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.144972320794191</v>
+        <v>-2.050541042541231</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.861239401417327</v>
+        <v>1.917898168369103</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.667215166513872</v>
+        <v>-8.752113661770332</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3186760731376137</v>
+        <v>-0.3526354712401978</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.104788022428</v>
+        <v>-2.010356744175041</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.885693604324883</v>
+        <v>1.942352371276658</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.587145370976067</v>
+        <v>-8.672043866232528</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2872813337017348</v>
+        <v>-0.3212407318043193</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.024718226890196</v>
+        <v>-1.930286948637236</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.933102302868322</v>
+        <v>1.989761069820098</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.353664148746468</v>
+        <v>-8.438562644002928</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1859644159720428</v>
+        <v>-0.2199238140746269</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.791237004660597</v>
+        <v>-1.696805726407638</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.081115465043934</v>
+        <v>2.137774231995709</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.203997757738954</v>
+        <v>-8.288896252995414</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1289900698819961</v>
+        <v>-0.1629494679845807</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.698333513418061</v>
+        <v>-1.603902235165102</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.133965349476496</v>
+        <v>2.190624116428272</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.071722284108066</v>
+        <v>-8.156620779364527</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.08071239368261418</v>
+        <v>-0.1146717917851987</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.566058039787175</v>
+        <v>-1.471626761534215</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.208698120402055</v>
+        <v>2.265356887353831</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.881122609434914</v>
+        <v>-7.966021104691374</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.001657463125716685</v>
+        <v>-0.03561686122830077</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.375458365114022</v>
+        <v>-1.281027086861062</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.325872985893583</v>
+        <v>2.382531752845359</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.632122810751333</v>
+        <v>-7.717021306007793</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1108487975713746</v>
+        <v>0.07688939946879048</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.375458365114022</v>
+        <v>-1.281027086861062</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.338779327117242</v>
+        <v>2.395438094069018</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.737712800524437</v>
+        <v>-7.822611295780898</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.05936312793708609</v>
+        <v>-0.09332252603967017</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.481048354887126</v>
+        <v>-1.386617076634167</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.147449403654161</v>
+        <v>2.204108170605937</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.756447702643034</v>
+        <v>-7.841346197899495</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.01831274690743845</v>
+        <v>-0.05227214501002253</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.481048354887126</v>
+        <v>-1.386617076634167</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.195993745531247</v>
+        <v>2.252652512483023</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.608507661235435</v>
+        <v>-7.693406156491895</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.0790156530325663</v>
+        <v>-0.1129750511351504</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.460727438978569</v>
+        <v>-1.366296160725609</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.088307372388214</v>
+        <v>2.14496613933999</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.584279024846462</v>
+        <v>-7.669177520102923</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.07803818473045521</v>
+        <v>-0.1119975828330397</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.436498802589596</v>
+        <v>-1.342067524336637</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.094130567968119</v>
+        <v>2.150789334919895</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.540730618075772</v>
+        <v>-7.625629113332232</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.06757943411727219</v>
+        <v>-0.1015388322198567</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.436498802589596</v>
+        <v>-1.342067524336637</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.087169955873026</v>
+        <v>2.143828722824802</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.298582224621914</v>
+        <v>-7.383480719878374</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.04374227764541416</v>
+        <v>0.009782879542829637</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.436498802589596</v>
+        <v>-1.342067524336637</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.101632310254169</v>
+        <v>2.158291077205945</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.235352852853565</v>
+        <v>-7.320251348110026</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.06356614681194817</v>
+        <v>0.02960674870936408</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.436498802589596</v>
+        <v>-1.342067524336637</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.096164430713364</v>
+        <v>2.15282319766514</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.112061718036434</v>
+        <v>-7.196960213292895</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1103806947493777</v>
+        <v>0.0764212966467932</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.313207667772466</v>
+        <v>-1.218776389519507</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.167637205614219</v>
+        <v>2.224295972565995</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.090912519132991</v>
+        <v>-7.175811014389452</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1265413525480801</v>
+        <v>0.092581954445496</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.292058468869023</v>
+        <v>-1.197627190616063</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.188027703193611</v>
+        <v>2.244686470145386</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.847147077149547</v>
+        <v>-6.932045572406007</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2198282376885086</v>
+        <v>0.185868839585924</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.292058468869023</v>
+        <v>-1.197627190616063</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.183808411540661</v>
+        <v>2.240467178492437</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.700250049431677</v>
+        <v>-6.785148544688138</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2807113626956723</v>
+        <v>0.2467519645930882</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.244400226890435</v>
+        <v>-1.149968948637475</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.21452767064783</v>
+        <v>2.271186437599606</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.450399655482602</v>
+        <v>-6.535298150739063</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3733935952590044</v>
+        <v>0.3394341971564203</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.244400226890435</v>
+        <v>-1.149968948637475</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.207269745631532</v>
+        <v>2.263928512583308</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.27450756301517</v>
+        <v>-6.359406058271631</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4473495557666261</v>
+        <v>0.4133901576640415</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.244400226890435</v>
+        <v>-1.149968948637475</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.210868869152181</v>
+        <v>2.267527636103956</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.103061099992707</v>
+        <v>-6.187959595249167</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.529255647030165</v>
+        <v>0.495296248927581</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.072953763867972</v>
+        <v>-0.978522485615012</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.327064253020212</v>
+        <v>2.383723019971988</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.878028100323884</v>
+        <v>-5.962926595580345</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6182893245139911</v>
+        <v>0.584329926411407</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8479207641991487</v>
+        <v>-0.7534894859461891</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.461104530437803</v>
+        <v>2.517763297389579</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.814392358089949</v>
+        <v>-5.89929085334641</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6484384224618824</v>
+        <v>0.6144790243592979</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7842850219652142</v>
+        <v>-0.6898537437122546</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.503980776832481</v>
+        <v>2.560639543784257</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.79881119554478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.718907369837223</v>
+        <v>-5.806290812140512</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6678266765467686</v>
+        <v>0.6328732996254529</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7842850219652142</v>
+        <v>-0.6898537437122546</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.485175035616277</v>
+        <v>2.541833802568052</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.478476873032363</v>
+        <v>-5.565860315335652</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.76574195189359</v>
+        <v>0.7307885749722747</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5438545251603539</v>
+        <v>-0.4494232469073943</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.63117641032407</v>
+        <v>2.687835177275846</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.406234304861168</v>
+        <v>-5.493617747164457</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.798568292996888</v>
+        <v>0.7636149160755727</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5438545251603539</v>
+        <v>-0.4494232469073943</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.63510572415889</v>
+        <v>2.691764491110666</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.290294455235983</v>
+        <v>-5.377677897539272</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8456228167643025</v>
+        <v>0.8106694398429868</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.46703279414423</v>
+        <v>-0.3726015158912704</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.681877346685905</v>
+        <v>2.73853611363768</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.04763886681282</v>
+        <v>-5.135022309116108</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9396831233535607</v>
+        <v>0.9047297464322455</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.46703279414423</v>
+        <v>-0.3726015158912704</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.678875417905898</v>
+        <v>2.735534184857674</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.827618068775809</v>
+        <v>-4.915001511079097</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.029270479578979</v>
+        <v>0.994317102657664</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3258129490762498</v>
+        <v>-0.2313816708232902</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.7651863619573</v>
+        <v>2.821845128909076</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.694750379712532</v>
+        <v>-4.78213382201582</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.098311738006114</v>
+        <v>1.063358361084798</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3258129490762498</v>
+        <v>-0.2313816708232902</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.781080544759124</v>
+        <v>2.8377393117109</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.535235276193162</v>
+        <v>-4.62261871849645</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.163263623854163</v>
+        <v>1.128310246932848</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1662978455568799</v>
+        <v>-0.07186656730392027</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.877935451311048</v>
+        <v>2.934594218262824</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.390563131093424</v>
+        <v>-4.477946573396713</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.231220584455498</v>
+        <v>1.196267207534183</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.02162570045714246</v>
+        <v>0.07280557779581714</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.97482684093233</v>
+        <v>3.031485607884106</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.450437958451117</v>
+        <v>-4.537821400754405</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.193308144913847</v>
+        <v>1.158354767992532</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.08150052781483458</v>
+        <v>0.01293075043812503</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.924939435919141</v>
+        <v>2.981598202870916</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.363638460672108</v>
+        <v>-4.451021902975397</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.250428437348017</v>
+        <v>1.215475060426701</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.08150052781483458</v>
+        <v>0.01293075043812503</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.947339929241707</v>
+        <v>3.003998696193483</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.366108167133914</v>
+        <v>-4.453491609437203</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.249512956136706</v>
+        <v>1.214559579215391</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.08397023427664074</v>
+        <v>0.01046104397631886</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.945930506738035</v>
+        <v>3.002589273689811</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.434478353457925</v>
+        <v>-4.521861795761213</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.233171804081804</v>
+        <v>1.198218427160489</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.0746945352404258</v>
+        <v>0.01973674301253381</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.962502848634466</v>
+        <v>3.019161615586242</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.313061923831448</v>
+        <v>-4.400445366134736</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.272175084564286</v>
+        <v>1.237221707642971</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.0746945352404258</v>
+        <v>0.01973674301253381</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.952939557266357</v>
+        <v>3.009598324218133</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.344055083160153</v>
+        <v>-4.431438525463442</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.084487385873191</v>
+        <v>1.049534008951876</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.0746945352404258</v>
+        <v>0.01973674301253381</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.777649122306744</v>
+        <v>2.83430788925852</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.168580823367684</v>
+        <v>-4.255964265670972</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.159244321781967</v>
+        <v>1.124290944860651</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.0746945352404258</v>
+        <v>0.01973674301253381</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.782216354298532</v>
+        <v>2.838875121250308</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.279517076008933</v>
+        <v>-4.366900518312221</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.090611849486674</v>
+        <v>1.055658472565359</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.0746945352404258</v>
+        <v>0.01973674301253381</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.757958383059739</v>
+        <v>2.814617150011515</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.482543653552166</v>
+        <v>-4.569927095855454</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.012532603689286</v>
+        <v>0.977579226767971</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2777211127836592</v>
+        <v>-0.1832898345306996</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.639273821753704</v>
+        <v>2.69593258870548</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.324618054616873</v>
+        <v>-4.412001496920161</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.085875229695536</v>
+        <v>1.050921852774221</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2777211127836592</v>
+        <v>-0.1832898345306996</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.649446208185837</v>
+        <v>2.706104975137613</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.238374591590495</v>
+        <v>-4.325758033893783</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.115318885479947</v>
+        <v>1.080365508558632</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2777211127836592</v>
+        <v>-0.1832898345306996</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.644392478759698</v>
+        <v>2.701051245711473</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.239557676241557</v>
+        <v>-4.326941118544845</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.106621427064048</v>
+        <v>1.071668050142733</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2833641612501707</v>
+        <v>-0.1889328829972111</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.632782425124316</v>
+        <v>2.689441192076092</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.116429969247474</v>
+        <v>-4.203813411550762</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.156424382894783</v>
+        <v>1.121471005973468</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2833641612501707</v>
+        <v>-0.1889328829972111</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.633334298157417</v>
+        <v>2.689993065109193</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.023619487796614</v>
+        <v>-4.111002930099902</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.122821267366493</v>
+        <v>1.087867890445177</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1905536797993114</v>
+        <v>-0.09612240154635177</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.618293278919299</v>
+        <v>2.674952045871074</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.975056435575584</v>
+        <v>-4.062439877878872</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.144119964179505</v>
+        <v>1.10916658725819</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1419906275782812</v>
+        <v>-0.04755934932532158</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.649304586176518</v>
+        <v>2.705963353128293</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.862385217339333</v>
+        <v>-3.949768659642622</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.184264159985728</v>
+        <v>1.149310783064413</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.02931940934203098</v>
+        <v>0.06511186891092863</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.711983025629991</v>
+        <v>2.768641792581767</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.750008216156661</v>
+        <v>-3.837391658459949</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.234706256289465</v>
+        <v>1.199752879368149</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.02931940934203098</v>
+        <v>0.06511186891092863</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.717474321460658</v>
+        <v>2.774133088412434</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.948242785043391</v>
+        <v>-4.03562622734668</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.166909630503312</v>
+        <v>1.131956253581996</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2275539782287616</v>
+        <v>-0.133122699975802</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.610030781897159</v>
+        <v>2.666689548848935</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.03124406606867</v>
+        <v>-4.118627508371959</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9720648380938535</v>
+        <v>0.937111461172538</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2461248627559353</v>
+        <v>-0.1516935845029757</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.437243971181508</v>
+        <v>2.493902738133284</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.872049794012093</v>
+        <v>-3.959433236315383</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.15589220763569</v>
+        <v>1.120938830714374</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2461248627559353</v>
+        <v>-0.1516935845029757</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.557393631900713</v>
+        <v>2.614052398852489</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.958648376993196</v>
+        <v>-4.046031819296486</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.135765800545572</v>
+        <v>1.100812423624256</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2461248627559353</v>
+        <v>-0.1516935845029757</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.571906658003036</v>
+        <v>2.628565424954812</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383423</v>
+        <v>3.741170494383424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.920264714435045</v>
+        <v>-4.007648156738335</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.148538706911201</v>
+        <v>1.113585329989885</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2077412001977841</v>
+        <v>-0.1133099219448245</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.592356296880296</v>
+        <v>2.649015063832072</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.743148384399879</v>
+        <v>-4.010915180443183</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.216114267770569</v>
+        <v>1.109007549353247</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2077412001977841</v>
+        <v>-0.1133099219448245</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.589085325725598</v>
+        <v>2.645744092677373</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.713446260423586</v>
+        <v>-3.981213056466889</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.228678509122999</v>
+        <v>1.121571790705678</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2122113254130975</v>
+        <v>-0.1177800471601379</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.587086642358323</v>
+        <v>2.643745409310099</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.534070839184817</v>
+        <v>-3.801837635228122</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.294215652924921</v>
+        <v>1.1871089345076</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.05543456724237883</v>
+        <v>0.03899671101058078</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.674939672567168</v>
+        <v>2.731598439518944</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.579085052705424</v>
+        <v>-3.846851848748728</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.257017422848268</v>
+        <v>1.149910704430947</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.08578346255698344</v>
+        <v>0.008647815695976169</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.637537790709995</v>
+        <v>2.694196557661771</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.846089562977859</v>
+        <v>-4.113856359021163</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.15590718107824</v>
+        <v>1.048800462660918</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.280146500599932</v>
+        <v>-0.1857152223469724</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.526611530223172</v>
+        <v>2.583270297174947</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.134876783436774</v>
+        <v>-4.402643579480078</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.039596214791175</v>
+        <v>0.9324894963738537</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3812326206989324</v>
+        <v>-0.2868013424459728</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.465163780060273</v>
+        <v>2.521822547012049</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.102401197266002</v>
+        <v>-4.370167993309306</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.050186410813801</v>
+        <v>0.9430796923964793</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3812326206989324</v>
+        <v>-0.2868013424459728</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.46276374161459</v>
+        <v>2.519422508566366</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.083363069558705</v>
+        <v>-4.351129865602009</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.054326381104965</v>
+        <v>0.947219662687643</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4394162320301269</v>
+        <v>-0.3449849537771673</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.424378294024118</v>
+        <v>2.481037060975894</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.10010893481508</v>
+        <v>-4.367875730858384</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.225209903941095</v>
+        <v>1.118103185523774</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4394162320301269</v>
+        <v>-0.3449849537771673</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.601960162962799</v>
+        <v>2.658618929914574</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.152429315415872</v>
+        <v>-4.420196111459176</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.205115080686912</v>
+        <v>1.09800836226959</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4044693720212548</v>
+        <v>-0.3100380937682952</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.623761607954255</v>
+        <v>2.680420374906031</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.296752221340791</v>
+        <v>-4.564519017384095</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.153394448713871</v>
+        <v>1.046287730296549</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4044693720212548</v>
+        <v>-0.3100380937682952</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.629770138351181</v>
+        <v>2.686428905302957</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989907</v>
+        <v>3.781497674989908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.149009251105788</v>
+        <v>-4.416776047149092</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.291644284599893</v>
+        <v>1.184537566182572</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2366620147863716</v>
+        <v>-0.142230736533412</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.809607200484133</v>
+        <v>2.866265967435909</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.755691284366996</v>
+        <v>3.440189442697933</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.947296864113548</v>
+        <v>2.743598039161883</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.149009251105788</v>
+        <v>-4.416776047149092</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.291644284599893</v>
+        <v>1.184537566182572</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2366620147863716</v>
+        <v>-0.142230736533412</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.940360661099916</v>
+        <v>2.73666183614825</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240517.xlsx
+++ b/tame_output/ON/bt/strategyON_20240517.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,32 +834,32 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-37.3%</t>
+          <t>-8.3%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.9%</t>
+          <t>-76.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>110.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.0%</t>
+          <t>-51.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.5%</t>
+          <t>-72.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>445.0%</t>
+          <t>448.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-10.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-603.3%</t>
+          <t>-565.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-34.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>344.8%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-257.8%</t>
+          <t>-242.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>-30.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-19.7%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-295.2%</t>
+          <t>-287.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-238.2%</t>
+          <t>-243.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.5%</t>
+          <t>-27.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-172.4%</t>
+          <t>-143.4%</t>
         </is>
       </c>
     </row>
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.635072811292202</v>
+        <v>-5.737481338317957</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8630389120924535</v>
+        <v>0.8220755012821512</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.6896061206682944</v>
+        <v>-0.7840373989212537</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.703660788522105</v>
+        <v>2.647002021570329</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.000200193930948</v>
+        <v>-5.990466262934998</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7162424740427862</v>
+        <v>0.7201360464411661</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.9859169049673069</v>
+        <v>-1.042560907351531</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.525128832948529</v>
+        <v>2.491142431517994</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.408788971111626</v>
+        <v>-6.399055040115677</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5515685071852738</v>
+        <v>0.5554620795836538</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.394505682147985</v>
+        <v>-1.45114968453221</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.278737110654881</v>
+        <v>2.244750709224346</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.82177145525272</v>
+        <v>-6.812037524256771</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3815609460002971</v>
+        <v>0.3854545183986766</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.394505682147985</v>
+        <v>-1.45114968453221</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.273922543126341</v>
+        <v>2.239936141695807</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.238163329539717</v>
+        <v>-7.228429398543768</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2129982468943754</v>
+        <v>0.2168918192927549</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.394505682147985</v>
+        <v>-1.45114968453221</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.271916593735219</v>
+        <v>2.237930192304684</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.614840340069562</v>
+        <v>-7.605106409073612</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.07258613335111663</v>
+        <v>0.07647970574949614</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.394505682147985</v>
+        <v>-1.45114968453221</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.282175284403898</v>
+        <v>2.248188882973363</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.96071516205437</v>
+        <v>-7.950981231058421</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.06966423029711155</v>
+        <v>-0.06577065789873204</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.394505682147985</v>
+        <v>-1.45114968453221</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.278274849549593</v>
+        <v>2.244288448119058</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.124295040238755</v>
+        <v>-8.114561109242805</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1366912615158644</v>
+        <v>-0.1327976891174845</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.394505682147985</v>
+        <v>-1.45114968453221</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.276679769604594</v>
+        <v>2.242693368174059</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.420956382048953</v>
+        <v>-8.411222451053003</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2515768223107355</v>
+        <v>-0.2476832499123556</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.463248817881864</v>
+        <v>-1.519892820266088</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.239212864093475</v>
+        <v>2.205226462662941</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.544200771264382</v>
+        <v>-8.534466840268433</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3049008825313102</v>
+        <v>-0.3010073101329307</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.463248817881864</v>
+        <v>-1.519892820266088</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.235186559559072</v>
+        <v>2.201200158128537</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.927202160007013</v>
+        <v>-8.917468229011064</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4582035393499471</v>
+        <v>-0.4543099669515671</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.463248817881864</v>
+        <v>-1.519892820266088</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.235084458237488</v>
+        <v>2.201098056806953</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.084601040220134</v>
+        <v>-9.074867109224185</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5185915754637649</v>
+        <v>-0.5146980030653854</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.620647698094985</v>
+        <v>-1.677291700479209</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.143216646081045</v>
+        <v>2.109230244650511</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.444131362724136</v>
+        <v>-9.434397431728186</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6570534011673157</v>
+        <v>-0.6531598287689357</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.620647698094985</v>
+        <v>-1.677291700479209</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.148566949379095</v>
+        <v>2.114580547948561</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.494480426178358</v>
+        <v>-9.484746495182408</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6692770065918268</v>
+        <v>-0.6653834341934473</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.670996761549207</v>
+        <v>-1.727640763933431</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.12627353126374</v>
+        <v>2.092287129833205</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.713629394252555</v>
+        <v>-9.703895463256606</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.753894843199737</v>
+        <v>-0.750001270801357</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.890145729623404</v>
+        <v>-1.946789732007629</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.99782590104099</v>
+        <v>1.963839499610455</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.709938469296144</v>
+        <v>-9.700204538300195</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7524184732171726</v>
+        <v>-0.7485249008187931</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.890145729623404</v>
+        <v>-1.946789732007629</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.99782590104099</v>
+        <v>1.963839499610455</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.914196644626008</v>
+        <v>-9.904462713630059</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.828608546230476</v>
+        <v>-0.824714973832096</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.017784674237393</v>
+        <v>-2.074428676621618</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.926755731391239</v>
+        <v>1.892769329960705</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.13223441625719</v>
+        <v>-10.12250048526124</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9113411003985106</v>
+        <v>-0.9074475280001306</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.192555442333292</v>
+        <v>-2.249199444717517</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.826375825018136</v>
+        <v>1.792389423587601</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.05876458458974</v>
+        <v>-10.04903065359379</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8665814662381104</v>
+        <v>-0.8626878938397304</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.119085610665844</v>
+        <v>-2.175729613050068</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.885829425512026</v>
+        <v>1.851843024081491</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.23388900197628</v>
+        <v>-10.22415507098033</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9220760124452108</v>
+        <v>-0.9181824400468308</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.294210028052388</v>
+        <v>-2.350854030436612</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.795309995827617</v>
+        <v>1.761323594397082</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.46834109599077</v>
+        <v>-10.45860716499482</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.023076014952603</v>
+        <v>-1.019182442554223</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.294210028052388</v>
+        <v>-2.350854030436612</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.788090830926021</v>
+        <v>1.754104429495486</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.75614494052801</v>
+        <v>-10.74641100953206</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.144869743541474</v>
+        <v>-1.140976171143094</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.582013872589626</v>
+        <v>-2.63865787497385</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.608736333429701</v>
+        <v>1.574749931999167</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.80893109612833</v>
+        <v>-10.79919716513239</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.164868415943048</v>
+        <v>-1.160974843544668</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.677689359172023</v>
+        <v>-2.734333361556247</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.55244683131882</v>
+        <v>1.518460429888285</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.0409600158646</v>
+        <v>-11.03122608486865</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.254986255208439</v>
+        <v>-1.251092682810059</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.739702056360446</v>
+        <v>-2.79634605874467</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.51793294163488</v>
+        <v>1.483946540204346</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.98894450189578</v>
+        <v>-10.97921057089983</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.230189713934513</v>
+        <v>-1.226296141536133</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.739702056360446</v>
+        <v>-2.79634605874467</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.521923277321281</v>
+        <v>1.487936875890747</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.1306163436199</v>
+        <v>-11.12088241262395</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.288333677522902</v>
+        <v>-1.284440105124522</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.739702056360446</v>
+        <v>-2.79634605874467</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.520448050422539</v>
+        <v>1.486461648992005</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.08102549919507</v>
+        <v>-11.07129156819912</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.253443929588097</v>
+        <v>-1.249550357189717</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.690111211935612</v>
+        <v>-2.746755214319836</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.565255967242312</v>
+        <v>1.531269565811777</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.88187339195797</v>
+        <v>-10.87213946096202</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.18683422033994</v>
+        <v>-1.18294064794156</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.524788685985799</v>
+        <v>-2.581432688370023</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.651398349165517</v>
+        <v>1.617411947734982</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.65602823923856</v>
+        <v>-10.64629430824261</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.086917086215966</v>
+        <v>-1.083023513817586</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.482862010398635</v>
+        <v>-2.539506012782859</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.686133427554024</v>
+        <v>1.652147026123489</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.53144958290097</v>
+        <v>-10.52171565190502</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.035946479124871</v>
+        <v>-1.032052906726491</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.482862010398635</v>
+        <v>-2.539506012782859</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.687272572110083</v>
+        <v>1.653286170679548</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.58434487094525</v>
+        <v>-10.5746109399493</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.054470820180478</v>
+        <v>-1.050577247782098</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.477906664310189</v>
+        <v>-2.534550666694413</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.692879553925258</v>
+        <v>1.658893152494723</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.3004361400165</v>
+        <v>-10.29070220902056</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9351736235703418</v>
+        <v>-0.9312800511719619</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.477906664310189</v>
+        <v>-2.534550666694413</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.698613258163895</v>
+        <v>1.66462685673336</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.22906974740686</v>
+        <v>-10.21933581641091</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9163643289203476</v>
+        <v>-0.9124707565219676</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.406540271700541</v>
+        <v>-2.463184274084765</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.731695831335818</v>
+        <v>1.697709429905284</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.965232880202787</v>
+        <v>-9.955498949206838</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8207130633516275</v>
+        <v>-0.8168194909532476</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.406540271700541</v>
+        <v>-2.463184274084765</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.72181235002291</v>
+        <v>1.687825948592376</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.885298101616605</v>
+        <v>-9.68825714833844</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7905737124165282</v>
+        <v>-0.7117573311052623</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.406540271700541</v>
+        <v>-2.463184274084765</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.719977789523537</v>
+        <v>1.685991388093002</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781946</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.787391062940115</v>
+        <v>-9.59035010966195</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7517112119193929</v>
+        <v>-0.672894830608127</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.338554521839985</v>
+        <v>-2.395198524224209</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.76046892446641</v>
+        <v>1.726482523035876</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.763437521964157</v>
+        <v>-9.566396568685992</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.741461289383516</v>
+        <v>-0.6626449080722501</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.314600980864027</v>
+        <v>-2.371244983248251</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.775509555197478</v>
+        <v>1.741523153766944</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487771</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.49937758364136</v>
+        <v>-9.302336630363195</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6490976302161497</v>
+        <v>-0.5702812489048834</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.050541042541231</v>
+        <v>-2.107185044925455</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.920685202029404</v>
+        <v>1.886698800598869</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309724</v>
+        <v>3.833249172309726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.792297960136523</v>
+        <v>-8.595257006858358</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3690528144745153</v>
+        <v>-0.2902364331632494</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.050541042541231</v>
+        <v>-2.107185044925455</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.917898168369103</v>
+        <v>1.883911766938568</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858727</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.752113661770332</v>
+        <v>-8.555072708492167</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3526354712401978</v>
+        <v>-0.2738190899289319</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.010356744175041</v>
+        <v>-2.067000746559264</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.942352371276658</v>
+        <v>1.908365969846124</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096473</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.672043866232528</v>
+        <v>-8.475002912954363</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3212407318043193</v>
+        <v>-0.242424350493053</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.930286948637236</v>
+        <v>-1.98693095102146</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.989761069820098</v>
+        <v>1.955774668389563</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.78732685376181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.438562644002928</v>
+        <v>-8.241521690724763</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2199238140746269</v>
+        <v>-0.141107432763361</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.696805726407638</v>
+        <v>-1.753449728791862</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.137774231995709</v>
+        <v>2.103787830565175</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.288896252995414</v>
+        <v>-8.091855299717249</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1629494679845807</v>
+        <v>-0.08413308667331432</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.603902235165102</v>
+        <v>-1.660546237549326</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.190624116428272</v>
+        <v>2.156637714997737</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860428</v>
+        <v>3.76317867286043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.156620779364527</v>
+        <v>-7.959579826086363</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1146717917851987</v>
+        <v>-0.03585541047393281</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.471626761534215</v>
+        <v>-1.528270763918439</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.265356887353831</v>
+        <v>2.231370485923296</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.966021104691374</v>
+        <v>-7.76898015141321</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.03561686122830077</v>
+        <v>0.04319952008296468</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.281027086861062</v>
+        <v>-1.337671089245286</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.382531752845359</v>
+        <v>2.348545351414825</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.717021306007793</v>
+        <v>-7.519980352729629</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.07688939946879048</v>
+        <v>0.1557057807800559</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.281027086861062</v>
+        <v>-1.337671089245286</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.395438094069018</v>
+        <v>2.361451692638483</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.822611295780898</v>
+        <v>-7.625570342502733</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.09332252603967017</v>
+        <v>-0.01450614472840428</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.386617076634167</v>
+        <v>-1.443261079018391</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.204108170605937</v>
+        <v>2.170121769175402</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.841346197899495</v>
+        <v>-7.64430524462133</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.05227214501002253</v>
+        <v>0.02654423630124292</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.386617076634167</v>
+        <v>-1.443261079018391</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.252652512483023</v>
+        <v>2.218666111052489</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.693406156491895</v>
+        <v>-7.496365203213731</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1129750511351504</v>
+        <v>-0.03415866982388494</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.366296160725609</v>
+        <v>-1.422940163109833</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.14496613933999</v>
+        <v>2.110979737909456</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879202</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.669177520102923</v>
+        <v>-7.472136566824759</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1119975828330397</v>
+        <v>-0.03318120152177384</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.342067524336637</v>
+        <v>-1.398711526720861</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.150789334919895</v>
+        <v>2.116802933489361</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.625629113332232</v>
+        <v>-7.428588160054068</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1015388322198567</v>
+        <v>-0.02272245090859082</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.342067524336637</v>
+        <v>-1.398711526720861</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.143828722824802</v>
+        <v>2.109842321394268</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963419</v>
+        <v>3.782918957963421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.383480719878374</v>
+        <v>-7.18643976660021</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.009782879542829637</v>
+        <v>0.08859926085409553</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.342067524336637</v>
+        <v>-1.398711526720861</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.158291077205945</v>
+        <v>2.124304675775411</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.320251348110026</v>
+        <v>-7.123210394831862</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.02960674870936408</v>
+        <v>0.10842313002063</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.342067524336637</v>
+        <v>-1.398711526720861</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.15282319766514</v>
+        <v>2.118836796234606</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.196960213292895</v>
+        <v>-6.999919260014731</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.0764212966467932</v>
+        <v>0.1552376779580591</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.218776389519507</v>
+        <v>-1.27542039190373</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.224295972565995</v>
+        <v>2.190309571135461</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389911</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.175811014389452</v>
+        <v>-6.978770061111288</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.092581954445496</v>
+        <v>0.1713983357567614</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.197627190616063</v>
+        <v>-1.254271193000287</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.244686470145386</v>
+        <v>2.210700068714852</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788094</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.932045572406007</v>
+        <v>-6.735004619127843</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.185868839585924</v>
+        <v>0.2646852208971899</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.197627190616063</v>
+        <v>-1.254271193000287</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.240467178492437</v>
+        <v>2.206480777061903</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.785148544688138</v>
+        <v>-6.588107591409972</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2467519645930882</v>
+        <v>0.3255683459043541</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.149968948637475</v>
+        <v>-1.206612951021699</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.271186437599606</v>
+        <v>2.237200036169071</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.826351398749185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.535298150739063</v>
+        <v>-6.338257197460898</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3394341971564203</v>
+        <v>0.4182505784676862</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.149968948637475</v>
+        <v>-1.206612951021699</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.263928512583308</v>
+        <v>2.229942111152774</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.359406058271631</v>
+        <v>-6.162365104993466</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4133901576640415</v>
+        <v>0.4922065389753079</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.149968948637475</v>
+        <v>-1.206612951021699</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.267527636103956</v>
+        <v>2.233541234673422</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.780930335862988</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.187959595249167</v>
+        <v>-5.990918641971002</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.495296248927581</v>
+        <v>0.5741126302388468</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.978522485615012</v>
+        <v>-1.035166487999236</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.383723019971988</v>
+        <v>2.349736618541454</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.962926595580345</v>
+        <v>-5.765885642302179</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.584329926411407</v>
+        <v>0.6631463077226729</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7534894859461891</v>
+        <v>-0.8101334883304131</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.517763297389579</v>
+        <v>2.483776895959044</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.764614304353074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.89929085334641</v>
+        <v>-5.702249900068245</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6144790243592979</v>
+        <v>0.6932954056705642</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.6898537437122546</v>
+        <v>-0.7464977460964786</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.560639543784257</v>
+        <v>2.526653142353723</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881119554478</v>
+        <v>3.798811195544782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.806290812140512</v>
+        <v>-5.609249858862347</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6328732996254529</v>
+        <v>0.7116896809367192</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.6898537437122546</v>
+        <v>-0.7464977460964786</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.541833802568052</v>
+        <v>2.507847401137518</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.797691308712294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.565860315335652</v>
+        <v>-5.368819362057486</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7307885749722747</v>
+        <v>0.8096049562835406</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4494232469073943</v>
+        <v>-0.5060672492916183</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.687835177275846</v>
+        <v>2.653848775845312</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837684</v>
+        <v>3.821589933837686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.493617747164457</v>
+        <v>-5.296576793886292</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7636149160755727</v>
+        <v>0.8424312973868386</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4494232469073943</v>
+        <v>-0.5060672492916183</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.691764491110666</v>
+        <v>2.657778089680132</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349966</v>
+        <v>3.822323422349967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.377677897539272</v>
+        <v>-5.180636944261106</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8106694398429868</v>
+        <v>0.8894858211542527</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3726015158912704</v>
+        <v>-0.4292455182754944</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.73853611363768</v>
+        <v>2.704549712207146</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861305097234</v>
+        <v>3.848613050972341</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.135022309116108</v>
+        <v>-4.937981355837943</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9047297464322455</v>
+        <v>0.9835461277435118</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3726015158912704</v>
+        <v>-0.4292455182754944</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.735534184857674</v>
+        <v>2.70154778342714</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.81866537614594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.915001511079097</v>
+        <v>-4.717960557800932</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.994317102657664</v>
+        <v>1.07313348396893</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2313816708232902</v>
+        <v>-0.2880256732075142</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.821845128909076</v>
+        <v>2.787858727478542</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327095200995</v>
+        <v>3.843270952009952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.78213382201582</v>
+        <v>-4.585092868737655</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.063358361084798</v>
+        <v>1.142174742396064</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2313816708232902</v>
+        <v>-0.2880256732075142</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.8377393117109</v>
+        <v>2.803752910280365</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966258</v>
+        <v>3.84504381096626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.62261871849645</v>
+        <v>-4.425577765218285</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.128310246932848</v>
+        <v>1.207126628244114</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.07186656730392027</v>
+        <v>-0.1285105696881442</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.934594218262824</v>
+        <v>2.900607816832289</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046996</v>
+        <v>3.791269976046998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.477946573396713</v>
+        <v>-4.280905620118547</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.196267207534183</v>
+        <v>1.275083588845449</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.07280557779581714</v>
+        <v>0.01616157541159319</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.031485607884106</v>
+        <v>2.997499206453571</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412104</v>
+        <v>3.735835647412106</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.537821400754405</v>
+        <v>-4.34078044747624</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.158354767992532</v>
+        <v>1.237171149303798</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.01293075043812503</v>
+        <v>-0.04371325194609893</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.981598202870916</v>
+        <v>2.947611801440382</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144515</v>
+        <v>3.762643902144517</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.451021902975397</v>
+        <v>-4.253980949697231</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.215475060426701</v>
+        <v>1.294291441737967</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.01293075043812503</v>
+        <v>-0.04371325194609893</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.003998696193483</v>
+        <v>2.970012294762948</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900693</v>
+        <v>3.729142822900695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.453491609437203</v>
+        <v>-4.256450656159037</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.214559579215391</v>
+        <v>1.293375960526657</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.01046104397631886</v>
+        <v>-0.04618295840790509</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.002589273689811</v>
+        <v>2.968602872259277</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432166204736</v>
+        <v>3.743216620473602</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.521861795761213</v>
+        <v>-4.324820842483048</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.198218427160489</v>
+        <v>1.277034808471755</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.01973674301253381</v>
+        <v>-0.03690725937169015</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.019161615586242</v>
+        <v>2.985175214155708</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978369</v>
+        <v>3.714175563978371</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.400445366134736</v>
+        <v>-4.203404412856571</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.237221707642971</v>
+        <v>1.316038088954237</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.01973674301253381</v>
+        <v>-0.03690725937169015</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.009598324218133</v>
+        <v>2.975611922787599</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887702</v>
+        <v>3.710903155887704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.431438525463442</v>
+        <v>-4.234397572185276</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.049534008951876</v>
+        <v>1.128350390263142</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.01973674301253381</v>
+        <v>-0.03690725937169015</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.83430788925852</v>
+        <v>2.800321487827986</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.7460389506759</v>
+        <v>3.746038950675902</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.255964265670972</v>
+        <v>-4.058923312392807</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.124290944860651</v>
+        <v>1.203107326171917</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.01973674301253381</v>
+        <v>-0.03690725937169015</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.838875121250308</v>
+        <v>2.804888719819774</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695446</v>
+        <v>3.765020747695448</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.366900518312221</v>
+        <v>-4.169859565034056</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.055658472565359</v>
+        <v>1.134474853876625</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.01973674301253381</v>
+        <v>-0.03690725937169015</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.814617150011515</v>
+        <v>2.780630748580981</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581291</v>
+        <v>3.773206721581293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.569927095855454</v>
+        <v>-4.372886142577289</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.977579226767971</v>
+        <v>1.056395608079237</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1832898345306996</v>
+        <v>-0.2399338369149235</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.69593258870548</v>
+        <v>2.661946187274946</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734161</v>
+        <v>3.784340376734162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.412001496920161</v>
+        <v>-4.214960543641996</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.050921852774221</v>
+        <v>1.129738234085487</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1832898345306996</v>
+        <v>-0.2399338369149235</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.706104975137613</v>
+        <v>2.672118573707079</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212297</v>
+        <v>3.786946382212299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.325758033893783</v>
+        <v>-4.128717080615618</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.080365508558632</v>
+        <v>1.159181889869898</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1832898345306996</v>
+        <v>-0.2399338369149235</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.701051245711473</v>
+        <v>2.667064844280939</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786044</v>
+        <v>3.752023923786046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.326941118544845</v>
+        <v>-4.12990016526668</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.071668050142733</v>
+        <v>1.150484431453999</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1889328829972111</v>
+        <v>-0.2455768853814351</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.689441192076092</v>
+        <v>2.655454790645557</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273191</v>
+        <v>3.753567590273192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.203813411550762</v>
+        <v>-4.006772458272597</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.121471005973468</v>
+        <v>1.200287387284734</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1889328829972111</v>
+        <v>-0.2455768853814351</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.689993065109193</v>
+        <v>2.656006663678659</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333870252795</v>
+        <v>3.733387025279502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.111002930099902</v>
+        <v>-3.913961976821737</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.087867890445177</v>
+        <v>1.166684271756443</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.09612240154635177</v>
+        <v>-0.1527664039305757</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.674952045871074</v>
+        <v>2.64096564444054</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030427</v>
+        <v>3.748282241030429</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.062439877878872</v>
+        <v>-3.865398924600707</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.10916658725819</v>
+        <v>1.187982968569456</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.04755934932532158</v>
+        <v>-0.1042033517095455</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.705963353128293</v>
+        <v>2.671976951697759</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942739</v>
+        <v>3.721073619942741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.949768659642622</v>
+        <v>-3.752727706364457</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.149310783064413</v>
+        <v>1.228127164375679</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.06511186891092863</v>
+        <v>0.00846786652670467</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.768641792581767</v>
+        <v>2.734655391151232</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268537</v>
+        <v>3.743044028268539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.837391658459949</v>
+        <v>-3.640350705181784</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.199752879368149</v>
+        <v>1.278569260679415</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.06511186891092863</v>
+        <v>0.00846786652670467</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.774133088412434</v>
+        <v>2.7401466869819</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968862</v>
+        <v>3.689594264968864</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.03562622734668</v>
+        <v>-3.838585274068515</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.131956253581996</v>
+        <v>1.210772634893262</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.133122699975802</v>
+        <v>-0.1897667023600259</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.666689548848935</v>
+        <v>2.6327031474184</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175322</v>
+        <v>3.643066046175324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.118627508371959</v>
+        <v>-3.921586555093794</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.937111461172538</v>
+        <v>1.015927842483804</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1516935845029757</v>
+        <v>-0.2083375868871997</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.493902738133284</v>
+        <v>2.459916336702749</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199269</v>
+        <v>3.682712735199271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.959433236315383</v>
+        <v>-3.762392283037217</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.120938830714374</v>
+        <v>1.19975521202564</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1516935845029757</v>
+        <v>-0.2083375868871997</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.614052398852489</v>
+        <v>2.580065997421955</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660769</v>
+        <v>3.733008865660771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.046031819296486</v>
+        <v>-3.84899086601832</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.100812423624256</v>
+        <v>1.179628804935522</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1516935845029757</v>
+        <v>-0.2083375868871997</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.628565424954812</v>
+        <v>2.594579023524278</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383424</v>
+        <v>3.741170494383426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.007648156738335</v>
+        <v>-3.810607203460169</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.113585329989885</v>
+        <v>1.192401711301151</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1133099219448245</v>
+        <v>-0.1699539243290485</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.649015063832072</v>
+        <v>2.615028662401537</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002484</v>
+        <v>3.751143622002486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.010915180443183</v>
+        <v>-3.633490873425003</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.109007549353247</v>
+        <v>1.259977272160519</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1133099219448245</v>
+        <v>-0.1699539243290485</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.645744092677373</v>
+        <v>2.611757691246839</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263903</v>
+        <v>3.741324873263904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.981213056466889</v>
+        <v>-3.60378874944871</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.121571790705678</v>
+        <v>1.27254151351295</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1177800471601379</v>
+        <v>-0.1744240495443619</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.643745409310099</v>
+        <v>2.609759007879564</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481236</v>
+        <v>3.750725801481238</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.801837635228122</v>
+        <v>-3.424413328209941</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.1871089345076</v>
+        <v>1.338078657314872</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.03899671101058078</v>
+        <v>-0.01764729137364318</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.731598439518944</v>
+        <v>2.69761203808841</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452231</v>
+        <v>3.716988143452233</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.846851848748728</v>
+        <v>-3.469427541730548</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.149910704430947</v>
+        <v>1.300880427238219</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.008647815695976169</v>
+        <v>-0.04799618668824779</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.694196557661771</v>
+        <v>2.660210156231237</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979538</v>
+        <v>3.73702303297954</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.113856359021163</v>
+        <v>-3.736432052002983</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.048800462660918</v>
+        <v>1.19977018546819</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1857152223469724</v>
+        <v>-0.2423592247311964</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.583270297174947</v>
+        <v>2.549283895744413</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230808</v>
+        <v>3.70230587923081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.402643579480078</v>
+        <v>-4.025219272461898</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9324894963738537</v>
+        <v>1.083459219181126</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2868013424459728</v>
+        <v>-0.3434453448301967</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.521822547012049</v>
+        <v>2.487836145581515</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285454</v>
+        <v>3.705568086285456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.370167993309306</v>
+        <v>-3.992743686291126</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9430796923964793</v>
+        <v>1.094049415203751</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2868013424459728</v>
+        <v>-0.3434453448301967</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.519422508566366</v>
+        <v>2.485436107135831</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848102</v>
+        <v>3.709506867848104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.351129865602009</v>
+        <v>-3.973705558583829</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.947219662687643</v>
+        <v>1.098189385494915</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3449849537771673</v>
+        <v>-0.4016289561613913</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.481037060975894</v>
+        <v>2.44705065954536</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601251</v>
+        <v>3.731060897601253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.367875730858384</v>
+        <v>-3.990451423840204</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.118103185523774</v>
+        <v>1.269072908331046</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3449849537771673</v>
+        <v>-0.4016289561613913</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.658618929914574</v>
+        <v>2.62463252848404</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537863</v>
+        <v>3.722443786537865</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.420196111459176</v>
+        <v>-4.042771804440996</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.09800836226959</v>
+        <v>1.248978085076863</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3100380937682952</v>
+        <v>-0.3666820961525191</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.680420374906031</v>
+        <v>2.646433973475497</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259122</v>
+        <v>3.787422005259124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.564519017384095</v>
+        <v>-4.187094710365915</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.046287730296549</v>
+        <v>1.197257453103821</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3100380937682952</v>
+        <v>-0.3666820961525191</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.686428905302957</v>
+        <v>2.652442503872423</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989908</v>
+        <v>3.781497674989909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.416776047149092</v>
+        <v>-4.039351740130912</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.184537566182572</v>
+        <v>1.335507288989844</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.142230736533412</v>
+        <v>-0.198874738917636</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.866265967435909</v>
+        <v>2.832279566005375</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.440189442697933</v>
+        <v>3.825765278950782</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.743598039161883</v>
+        <v>3.033370389674982</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.416776047149092</v>
+        <v>-4.039351740130912</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.184537566182572</v>
+        <v>1.335507288989844</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.142230736533412</v>
+        <v>-0.198874738917636</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.73666183614825</v>
+        <v>3.02643418666135</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240517.xlsx
+++ b/tame_output/ON/bt/strategyON_20240517.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>46.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,22 +824,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-20.9%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-77.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.2%</t>
+          <t>110.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.5%</t>
+          <t>129.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.3%</t>
+          <t>-51.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.3%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.8%</t>
+          <t>448.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-565.5%</t>
+          <t>-592.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.0%</t>
+          <t>-37.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-34.6%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>140.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-242.7%</t>
+          <t>-258.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-28.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.4%</t>
+          <t>-30.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-22.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-287.4%</t>
+          <t>-144.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-243.9%</t>
+          <t>-266.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.8%</t>
+          <t>-24.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-14.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-143.4%</t>
+          <t>-180.8%</t>
         </is>
       </c>
     </row>
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.990466262934998</v>
+        <v>-6.102608720956703</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7201360464411661</v>
+        <v>0.6752790632324839</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.042560907351531</v>
+        <v>-1.080348183220266</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.491142431517994</v>
+        <v>2.468470065996753</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330522</v>
       </c>
       <c r="C1864" t="n">
-        <v>3.115440519943672</v>
+        <v>3.426155199561141</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.399055040115677</v>
+        <v>-6.511197498137381</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5554620795836538</v>
+        <v>0.8213197759924413</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.45114968453221</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.244750709224346</v>
+        <v>2.532793023320575</v>
       </c>
     </row>
     <row r="1865">
@@ -44443,19 +44443,19 @@
         <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
-        <v>3.110625952415132</v>
+        <v>3.421340632032601</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.812037524256771</v>
+        <v>-6.924179982278475</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3854545183986766</v>
+        <v>0.6513122148074637</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.45114968453221</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.239936141695807</v>
+        <v>2.527978455792035</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108639</v>
       </c>
       <c r="C1866" t="n">
-        <v>3.10862000302401</v>
+        <v>3.419334682641479</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.228429398543768</v>
+        <v>-7.340571856565473</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2168918192927549</v>
+        <v>0.482749515701542</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.45114968453221</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.237930192304684</v>
+        <v>2.525972506400912</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
-        <v>3.118878693692689</v>
+        <v>3.429593373310158</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.605106409073612</v>
+        <v>-7.717248867095317</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.07647970574949614</v>
+        <v>0.3423374021582832</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.45114968453221</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.248188882973363</v>
+        <v>2.536231197069591</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
-        <v>3.114978258838384</v>
+        <v>3.425692938455853</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.950981231058421</v>
+        <v>-8.063123689080125</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.06577065789873204</v>
+        <v>0.200087038510055</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.45114968453221</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.244288448119058</v>
+        <v>2.532330762215286</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
-        <v>3.113383178893385</v>
+        <v>3.424097858510854</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.114561109242805</v>
+        <v>-8.22670356726451</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1327976891174845</v>
+        <v>0.1330600072913026</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.45114968453221</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.242693368174059</v>
+        <v>2.530735682270287</v>
       </c>
     </row>
     <row r="1870">
@@ -44558,19 +44558,19 @@
         <v>3.424633354969594</v>
       </c>
       <c r="C1870" t="n">
-        <v>3.117162154822593</v>
+        <v>3.427876834440062</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.411222451053003</v>
+        <v>-8.523364909074708</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2476832499123556</v>
+        <v>0.01817444649643152</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.519892820266088</v>
+        <v>-1.557680096134823</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.205226462662941</v>
+        <v>2.493268776759168</v>
       </c>
     </row>
     <row r="1871">
@@ -44581,19 +44581,19 @@
         <v>3.419979433923088</v>
       </c>
       <c r="C1871" t="n">
-        <v>3.11313585028819</v>
+        <v>3.423850529905659</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.534466840268433</v>
+        <v>-8.646609298290137</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3010073101329307</v>
+        <v>-0.0351496137241436</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.519892820266088</v>
+        <v>-1.557680096134823</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.201200158128537</v>
+        <v>2.489242472224765</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
-        <v>3.113033748966606</v>
+        <v>3.423748428584075</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.917468229011064</v>
+        <v>-9.029610687032768</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4543099669515671</v>
+        <v>-0.18845227054278</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.519892820266088</v>
+        <v>-1.557680096134823</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.201098056806953</v>
+        <v>2.489140370903181</v>
       </c>
     </row>
     <row r="1873">
@@ -44627,19 +44627,19 @@
         <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
-        <v>3.115605264938036</v>
+        <v>3.426319944555505</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.074867109224185</v>
+        <v>-9.187009567245889</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5146980030653854</v>
+        <v>-0.2488403066565983</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.677291700479209</v>
+        <v>-1.715078976347944</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.109230244650511</v>
+        <v>2.397272558746739</v>
       </c>
     </row>
     <row r="1874">
@@ -44650,19 +44650,19 @@
         <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
-        <v>3.120955568236086</v>
+        <v>3.431670247853555</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.434397431728186</v>
+        <v>-9.546539889749891</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6531598287689357</v>
+        <v>-0.3873021323601487</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.677291700479209</v>
+        <v>-1.715078976347944</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.114580547948561</v>
+        <v>2.402622862044788</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
-        <v>3.128871588193264</v>
+        <v>3.439586267810733</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.484746495182408</v>
+        <v>-9.596888953204113</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6653834341934473</v>
+        <v>-0.3995257377846602</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.727640763933431</v>
+        <v>-1.765428039802166</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.092287129833205</v>
+        <v>2.380329443929433</v>
       </c>
     </row>
     <row r="1876">
@@ -44696,19 +44696,19 @@
         <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
-        <v>3.131913338815032</v>
+        <v>3.442628018432501</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.703895463256606</v>
+        <v>-9.81603792127831</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.750001270801357</v>
+        <v>-0.4841435743925699</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.946789732007629</v>
+        <v>-1.984577007876364</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.963839499610455</v>
+        <v>2.251881813706683</v>
       </c>
     </row>
     <row r="1877">
@@ -44719,19 +44719,19 @@
         <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.131913338815032</v>
+        <v>3.442628018432501</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.700204538300195</v>
+        <v>-9.812346996321899</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7485249008187931</v>
+        <v>-0.482667204410006</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.946789732007629</v>
+        <v>-1.984577007876364</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.963839499610455</v>
+        <v>2.251881813706683</v>
       </c>
     </row>
     <row r="1878">
@@ -44742,19 +44742,19 @@
         <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.137426535933675</v>
+        <v>3.448141215551144</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.904462713630059</v>
+        <v>-10.01660517165176</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.824714973832096</v>
+        <v>-0.5588572774233089</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.074428676621618</v>
+        <v>-2.112215952490353</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.892769329960705</v>
+        <v>2.180811644056933</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.141909090418111</v>
+        <v>3.45262377003558</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.12250048526124</v>
+        <v>-10.23464294328294</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9074475280001306</v>
+        <v>-0.6415898315913435</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.249199444717517</v>
+        <v>-2.286986720586252</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.792389423587601</v>
+        <v>2.080431737683829</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.157280791911532</v>
+        <v>3.467995471529001</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.04903065359379</v>
+        <v>-10.16117311161549</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8626878938397304</v>
+        <v>-0.5968301974309433</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.175729613050068</v>
+        <v>-2.213516888918803</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.851843024081491</v>
+        <v>2.139885338177719</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078599</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.171836012659049</v>
+        <v>3.482550692276518</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.22415507098033</v>
+        <v>-10.33629752900204</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9181824400468308</v>
+        <v>-0.6523247436380437</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.350854030436612</v>
+        <v>-2.388641306305347</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.761323594397082</v>
+        <v>2.04936590849331</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.164616847757453</v>
+        <v>3.475331527374922</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.45860716499482</v>
+        <v>-10.57074962301652</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.019182442554223</v>
+        <v>-0.7533247461454358</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.350854030436612</v>
+        <v>-2.388641306305347</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.754104429495486</v>
+        <v>2.042146743591714</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.157944656983477</v>
+        <v>3.468659336600945</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.74641100953206</v>
+        <v>-10.85855346755376</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.140976171143094</v>
+        <v>-0.875118474734307</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.63865787497385</v>
+        <v>-2.676445150842585</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.574749931999167</v>
+        <v>1.862792246095395</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.159060446822033</v>
+        <v>3.469775126439502</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.79919716513239</v>
+        <v>-10.91133962315409</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.160974843544668</v>
+        <v>-0.8951171471358812</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.734333361556247</v>
+        <v>-2.772120637424982</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.518460429888285</v>
+        <v>1.806502743984513</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.161754175451148</v>
+        <v>3.472468855068616</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.03122608486865</v>
+        <v>-11.14336854289035</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.251092682810059</v>
+        <v>-0.9852349864012715</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.79634605874467</v>
+        <v>-2.834133334613405</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.483946540204346</v>
+        <v>1.771988854300574</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.165744511137548</v>
+        <v>3.476459190755017</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.97921057089983</v>
+        <v>-11.09135302892154</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.226296141536133</v>
+        <v>-0.9604384451273456</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.79634605874467</v>
+        <v>-2.834133334613405</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.487936875890747</v>
+        <v>1.775979189986974</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.164269284238807</v>
+        <v>3.474983963856276</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.12088241262395</v>
+        <v>-11.23302487064566</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.284440105124522</v>
+        <v>-1.018582408715735</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.79634605874467</v>
+        <v>-2.834133334613405</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.486461648992005</v>
+        <v>1.774503963088233</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.179322694403679</v>
+        <v>3.490037374021148</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.07129156819912</v>
+        <v>-11.18343402622082</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.249550357189717</v>
+        <v>-0.9836926607809295</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.746755214319836</v>
+        <v>-2.784542490188572</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.531269565811777</v>
+        <v>1.819311879908005</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.166271560756996</v>
+        <v>3.476986240374465</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.87213946096202</v>
+        <v>-10.98428191898373</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.18294064794156</v>
+        <v>-0.9170829515327727</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.581432688370023</v>
+        <v>-2.619219964238758</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.617411947734982</v>
+        <v>1.90545426183121</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.175850633793205</v>
+        <v>3.486565313410674</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.64629430824261</v>
+        <v>-10.75843676626431</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.083023513817586</v>
+        <v>-0.817165817408799</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.539506012782859</v>
+        <v>-2.577293288651595</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.652147026123489</v>
+        <v>1.940189340219717</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.176989778349264</v>
+        <v>3.487704457966732</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.52171565190502</v>
+        <v>-10.63385810992672</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.032052906726491</v>
+        <v>-0.7661952103177039</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.539506012782859</v>
+        <v>-2.577293288651595</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.653286170679548</v>
+        <v>1.941328484775776</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.179623552511371</v>
+        <v>3.49033823212884</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.5746109399493</v>
+        <v>-10.68675339797101</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.050577247782098</v>
+        <v>-0.7847195513733105</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.534550666694413</v>
+        <v>-2.572337942563149</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.658893152494723</v>
+        <v>1.946935466590952</v>
       </c>
     </row>
     <row r="1893">
@@ -45087,19 +45087,19 @@
         <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.185357256750008</v>
+        <v>3.496071936367477</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.29070220902056</v>
+        <v>-10.40284466704226</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9312800511719619</v>
+        <v>-0.6654223547631748</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.534550666694413</v>
+        <v>-2.572337942563149</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.66462685673336</v>
+        <v>1.952669170829588</v>
       </c>
     </row>
     <row r="1894">
@@ -45110,19 +45110,19 @@
         <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.175619994356143</v>
+        <v>3.486334673973611</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.21933581641091</v>
+        <v>-10.33147827443261</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9124707565219676</v>
+        <v>-0.6466130601131805</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.463184274084765</v>
+        <v>-2.500971549953501</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.697709429905284</v>
+        <v>1.985751744001512</v>
       </c>
     </row>
     <row r="1895">
@@ -45133,19 +45133,19 @@
         <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.165736513043235</v>
+        <v>3.476451192660704</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.955498949206838</v>
+        <v>-10.06764140722854</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8168194909532476</v>
+        <v>-0.5509617945444609</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.463184274084765</v>
+        <v>-2.500971549953501</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.687825948592376</v>
+        <v>1.975868262688603</v>
       </c>
     </row>
     <row r="1896">
@@ -45156,19 +45156,19 @@
         <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.163901952543861</v>
+        <v>3.47461663216133</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.68825714833844</v>
+        <v>-9.800399606360145</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7117573311052623</v>
+        <v>-0.4458996346964752</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.463184274084765</v>
+        <v>-2.500971549953501</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.685991388093002</v>
+        <v>1.97403370218923</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781946</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.1636016375704</v>
+        <v>3.474316317187869</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.59035010966195</v>
+        <v>-9.702492567683654</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.672894830608127</v>
+        <v>-0.40703713419934</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.395198524224209</v>
+        <v>-2.432985800092944</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.726482523035876</v>
+        <v>2.014524837132103</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.164270143715894</v>
+        <v>3.474984823333363</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.566396568685992</v>
+        <v>-9.678539026707696</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6626449080722501</v>
+        <v>-0.396787211663463</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.371244983248251</v>
+        <v>-2.409032259116987</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.741523153766944</v>
+        <v>2.029565467863171</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.78930753648777</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.151009827554142</v>
+        <v>3.461724507171611</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.302336630363195</v>
+        <v>-9.414479088384899</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5702812489048834</v>
+        <v>-0.3044235524960963</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.107185044925455</v>
+        <v>-2.144972320794191</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.886698800598869</v>
+        <v>2.174741114695097</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309726</v>
+        <v>3.833249172309724</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.148222793893841</v>
+        <v>3.45893747351131</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.595257006858358</v>
+        <v>-8.707399464880062</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2902364331632494</v>
+        <v>-0.02437873675446234</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.107185044925455</v>
+        <v>-2.144972320794191</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.883911766938568</v>
+        <v>2.171954081034796</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.839370871858727</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.148566417781682</v>
+        <v>3.459281097399151</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.555072708492167</v>
+        <v>-8.667215166513872</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2738190899289319</v>
+        <v>-0.007961393520144799</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.067000746559264</v>
+        <v>-2.104788022428</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.908365969846124</v>
+        <v>2.196408283942351</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096472</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.147933239002439</v>
+        <v>3.458647918619908</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.475002912954363</v>
+        <v>-8.587145370976067</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.242424350493053</v>
+        <v>0.02343334591573409</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.98693095102146</v>
+        <v>-2.024718226890196</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.955774668389563</v>
+        <v>2.243816982485791</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78732685376181</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.155857667840292</v>
+        <v>3.466572347457761</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.241521690724763</v>
+        <v>-8.353664148746468</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.141107432763361</v>
+        <v>0.1247502636454261</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.753449728791862</v>
+        <v>-1.791237004660597</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.103787830565175</v>
+        <v>2.391830144661403</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255787</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.152965457527332</v>
+        <v>3.463680137144801</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.091855299717249</v>
+        <v>-8.203997757738954</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.08413308667331432</v>
+        <v>0.1817246097354728</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.660546237549326</v>
+        <v>-1.698333513418061</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.156637714997737</v>
+        <v>2.444680029093965</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76317867286043</v>
+        <v>3.763178672860428</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.14833294427436</v>
+        <v>3.459047623891828</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.959579826086363</v>
+        <v>-8.071722284108066</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.03585541047393281</v>
+        <v>0.2300022859348547</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.528270763918439</v>
+        <v>-1.566058039787175</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.231370485923296</v>
+        <v>2.519412800019524</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575955</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.151148004961996</v>
+        <v>3.461862684579465</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.76898015141321</v>
+        <v>-7.881122609434914</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.04319952008296468</v>
+        <v>0.3090572164917522</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.337671089245286</v>
+        <v>-1.375458365114022</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.348545351414825</v>
+        <v>2.636587665511052</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430989</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.164054346185655</v>
+        <v>3.474769025803124</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.519980352729629</v>
+        <v>-7.632122810751333</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1557057807800559</v>
+        <v>0.4215634771888435</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.337671089245286</v>
+        <v>-1.375458365114022</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.361451692638483</v>
+        <v>2.649494006734711</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.036078416586436</v>
+        <v>3.346793096203905</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.625570342502733</v>
+        <v>-7.737712800524437</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.01450614472840428</v>
+        <v>0.2513515516803828</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.443261079018391</v>
+        <v>-1.481048354887126</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.170121769175402</v>
+        <v>2.45816408327163</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.084622758463523</v>
+        <v>3.395337438080992</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.64430524462133</v>
+        <v>-7.756447702643034</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.02654423630124292</v>
+        <v>0.2924019327100305</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.443261079018391</v>
+        <v>-1.481048354887126</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.218666111052489</v>
+        <v>2.506708425148716</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.964743835775355</v>
+        <v>3.275458515392824</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.496365203213731</v>
+        <v>-7.608507661235435</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.03415866982388494</v>
+        <v>0.2316990265849026</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.422940163109833</v>
+        <v>-1.460727438978569</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.110979737909456</v>
+        <v>2.399022052005683</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879202</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.956029849521877</v>
+        <v>3.266744529139346</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.472136566824759</v>
+        <v>-7.584279024846462</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.03318120152177384</v>
+        <v>0.2326764948870137</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.398711526720861</v>
+        <v>-1.436498802589596</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.116802933489361</v>
+        <v>2.404845247585588</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568109</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.949069237426784</v>
+        <v>3.259783917044253</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.428588160054068</v>
+        <v>-7.540730618075772</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.02272245090859082</v>
+        <v>0.2431352455001967</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.398711526720861</v>
+        <v>-1.436498802589596</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.109842321394268</v>
+        <v>2.397884635490495</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963421</v>
+        <v>3.782918957963419</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.963531591807927</v>
+        <v>3.274246271425396</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.18643976660021</v>
+        <v>-7.298582224621914</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.08859926085409553</v>
+        <v>0.3544569572628831</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.398711526720861</v>
+        <v>-1.436498802589596</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.124304675775411</v>
+        <v>2.412346989871638</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192819</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.958063712267122</v>
+        <v>3.268778391884591</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.123210394831862</v>
+        <v>-7.235352852853565</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.10842313002063</v>
+        <v>0.3742808264294171</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.398711526720861</v>
+        <v>-1.436498802589596</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.118836796234606</v>
+        <v>2.406879110330833</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262049</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.955561806277699</v>
+        <v>3.266276485895168</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.999919260014731</v>
+        <v>-7.112061718036434</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1552376779580591</v>
+        <v>0.4210953743668466</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.27542039190373</v>
+        <v>-1.313207667772466</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.190309571135461</v>
+        <v>2.478351885231688</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389911</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.963262784515024</v>
+        <v>3.273977464132493</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.978770061111288</v>
+        <v>-7.090912519132991</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1713983357567614</v>
+        <v>0.437256032165549</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.254271193000287</v>
+        <v>-1.292058468869023</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.210700068714852</v>
+        <v>2.49874238281108</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788096</v>
+        <v>3.748324832788094</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.959043492862075</v>
+        <v>3.269758172479543</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.735004619127843</v>
+        <v>-6.847147077149547</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2646852208971899</v>
+        <v>0.5305429173059775</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.254271193000287</v>
+        <v>-1.292058468869023</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.206480777061903</v>
+        <v>2.49452309115813</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527527</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.961167806782091</v>
+        <v>3.271882486399559</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.588107591409972</v>
+        <v>-6.700250049431677</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3255683459043541</v>
+        <v>0.5914260423131412</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.206612951021699</v>
+        <v>-1.244400226890435</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.237200036169071</v>
+        <v>2.525242350265299</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749185</v>
+        <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.953909881765793</v>
+        <v>3.264624561383262</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.338257197460898</v>
+        <v>-6.450399655482602</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4182505784676862</v>
+        <v>0.6841082748764733</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.206612951021699</v>
+        <v>-1.244400226890435</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.229942111152774</v>
+        <v>2.517984425249001</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481497</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.957509005286441</v>
+        <v>3.26822368490391</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.162365104993466</v>
+        <v>-6.27450756301517</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4922065389753079</v>
+        <v>0.758064235384095</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.206612951021699</v>
+        <v>-1.244400226890435</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.233541234673422</v>
+        <v>2.52158354876965</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862988</v>
+        <v>3.780930335862986</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.970836511340995</v>
+        <v>3.281551190958464</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.990918641971002</v>
+        <v>-6.103061099992707</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5741126302388468</v>
+        <v>0.8399703266476339</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.035166487999236</v>
+        <v>-1.072953763867972</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.349736618541454</v>
+        <v>2.637778932637681</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.969856988957292</v>
+        <v>3.280571668574761</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.765885642302179</v>
+        <v>-5.878028100323884</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6631463077226729</v>
+        <v>0.92900400413146</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8101334883304131</v>
+        <v>-0.8479207641991487</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.483776895959044</v>
+        <v>2.771819210055272</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353074</v>
+        <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.974551790011609</v>
+        <v>3.285266469629078</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.702249900068245</v>
+        <v>-5.814392358089949</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6932954056705642</v>
+        <v>0.9591531020793513</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7464977460964786</v>
+        <v>-0.7842850219652142</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.526653142353723</v>
+        <v>2.81469545644995</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544782</v>
+        <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.955746048795405</v>
+        <v>3.266460728412874</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.609249858862347</v>
+        <v>-5.721392316884051</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7116896809367192</v>
+        <v>0.9775473773455063</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7464977460964786</v>
+        <v>-0.7842850219652142</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.507847401137518</v>
+        <v>2.795889715233746</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712294</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.957489125420282</v>
+        <v>3.268203805037751</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.368819362057486</v>
+        <v>-5.642484528317248</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8096049562835406</v>
+        <v>1.010853569397105</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5060672492916183</v>
+        <v>-0.7053772333984109</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.653848775845312</v>
+        <v>2.844977464998705</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837686</v>
+        <v>3.821589933837683</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.961418439255103</v>
+        <v>3.272133118872572</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.296576793886292</v>
+        <v>-5.570241960146054</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8424312973868386</v>
+        <v>1.043679910500403</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5060672492916183</v>
+        <v>-0.7053772333984109</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.657778089680132</v>
+        <v>2.848906778833525</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349967</v>
+        <v>3.822323422349965</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.962097023172443</v>
+        <v>3.272811702789912</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.180636944261106</v>
+        <v>-5.454302110520868</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8894858211542527</v>
+        <v>1.090734434267817</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.4292455182754944</v>
+        <v>-0.628555502382287</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.704549712207146</v>
+        <v>2.89567840136054</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972341</v>
+        <v>3.848613050972339</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.959095094392436</v>
+        <v>3.269809774009905</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.937981355837943</v>
+        <v>-5.211646522097706</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9835461277435118</v>
+        <v>1.184794740857075</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.4292455182754944</v>
+        <v>-0.628555502382287</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.70154778342714</v>
+        <v>2.892676472580533</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866537614594</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.96067413140305</v>
+        <v>3.271388811020519</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.717960557800932</v>
+        <v>-4.991625724060695</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.07313348396893</v>
+        <v>1.274382097082494</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2880256732075142</v>
+        <v>-0.4873356573143067</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.787858727478542</v>
+        <v>2.978987416631935</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009952</v>
+        <v>3.84327095200995</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.976568314204874</v>
+        <v>3.287282993822342</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.585092868737655</v>
+        <v>-4.858758034997417</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.142174742396064</v>
+        <v>1.343423355509628</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2880256732075142</v>
+        <v>-0.4873356573143067</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.803752910280365</v>
+        <v>2.994881599433759</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.84504381096626</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.977714158645175</v>
+        <v>3.288428838262644</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.425577765218285</v>
+        <v>-4.699242931478048</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.207126628244114</v>
+        <v>1.408375241357678</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1285105696881442</v>
+        <v>-0.3278205537949368</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.900607816832289</v>
+        <v>3.091736505985683</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791269976046998</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.987802261206615</v>
+        <v>3.298516940824084</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.280905620118547</v>
+        <v>-4.55457078637831</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.275083588845449</v>
+        <v>1.476332201959013</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.01616157541159319</v>
+        <v>-0.1831484086951994</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.997499206453571</v>
+        <v>3.188627895606965</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735835647412106</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.973839752608041</v>
+        <v>3.28455443222551</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.34078044747624</v>
+        <v>-4.614445613736002</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.237171149303798</v>
+        <v>1.438419762417362</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.04371325194609893</v>
+        <v>-0.2430232360528915</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.947611801440382</v>
+        <v>3.138740490593775</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762643902144517</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.996240245930607</v>
+        <v>3.306954925548076</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.253980949697231</v>
+        <v>-4.527646115956994</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.294291441737967</v>
+        <v>1.495540054851531</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.04371325194609893</v>
+        <v>-0.2430232360528915</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.970012294762948</v>
+        <v>3.161140983916341</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729142822900695</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.996312647304019</v>
+        <v>3.307027326921488</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.256450656159037</v>
+        <v>-4.5301158224188</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.293375960526657</v>
+        <v>1.494624573640221</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.04618295840790509</v>
+        <v>-0.2454929425146977</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.968602872259277</v>
+        <v>3.15973156141267</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743216620473602</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.007319569778721</v>
+        <v>3.31803424939619</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.324820842483048</v>
+        <v>-4.59848600874281</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.277034808471755</v>
+        <v>1.478283421585319</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.03690725937169015</v>
+        <v>-0.2362172434784827</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.985175214155708</v>
+        <v>3.176303903309101</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714175563978371</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.997756278410613</v>
+        <v>3.308470958028082</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.203404412856571</v>
+        <v>-4.477069579116334</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.316038088954237</v>
+        <v>1.517286702067801</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.03690725937169015</v>
+        <v>-0.2362172434784827</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.975611922787599</v>
+        <v>3.166740611940992</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887704</v>
+        <v>3.710903155887703</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.822465843450999</v>
+        <v>3.133180523068468</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.234397572185276</v>
+        <v>-4.508062738445039</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.128350390263142</v>
+        <v>1.329599003376706</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.03690725937169015</v>
+        <v>-0.2362172434784827</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.800321487827986</v>
+        <v>2.991450176981379</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675902</v>
+        <v>3.7460389506759</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.827033075442787</v>
+        <v>3.137747755060256</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.058923312392807</v>
+        <v>-4.332588478652569</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.203107326171917</v>
+        <v>1.404355939285481</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.03690725937169015</v>
+        <v>-0.2362172434784827</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.804888719819774</v>
+        <v>2.996017408973167</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695448</v>
+        <v>3.765020747695446</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.802775104203994</v>
+        <v>3.113489783821463</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.169859565034056</v>
+        <v>-4.443524731293818</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.134474853876625</v>
+        <v>1.335723466990189</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.03690725937169015</v>
+        <v>-0.2362172434784827</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.780630748580981</v>
+        <v>2.971759437734374</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773206721581293</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.8059064894239</v>
+        <v>3.116621169041369</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.372886142577289</v>
+        <v>-4.646551308837052</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.056395608079237</v>
+        <v>1.257644221192801</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2399338369149235</v>
+        <v>-0.4392438210217161</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.661946187274946</v>
+        <v>2.85307487642834</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784340376734162</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.816078875856032</v>
+        <v>3.126793555473501</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.214960543641996</v>
+        <v>-4.488625709901759</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.129738234085487</v>
+        <v>1.33098684719905</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2399338369149235</v>
+        <v>-0.4392438210217161</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.672118573707079</v>
+        <v>2.863247262860472</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786946382212299</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.811025146429893</v>
+        <v>3.121739826047361</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.128717080615618</v>
+        <v>-4.402382246875381</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.159181889869898</v>
+        <v>1.360430502983462</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2399338369149235</v>
+        <v>-0.4392438210217161</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.667064844280939</v>
+        <v>2.858193533434332</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752023923786046</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.802800921874418</v>
+        <v>3.113515601491887</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.12990016526668</v>
+        <v>-4.403565331526442</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.150484431453999</v>
+        <v>1.351733044567563</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2455768853814351</v>
+        <v>-0.4448868694882276</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.655454790645557</v>
+        <v>2.846583479798951</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753567590273192</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.80335279490752</v>
+        <v>3.114067474524989</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.006772458272597</v>
+        <v>-4.280437624532359</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.200287387284734</v>
+        <v>1.401536000398298</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2455768853814351</v>
+        <v>-0.4448868694882276</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.656006663678659</v>
+        <v>2.847135352832052</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733387025279502</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.732625486798885</v>
+        <v>3.043340166416354</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.913961976821737</v>
+        <v>-4.1876271430815</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.166684271756443</v>
+        <v>1.367932884870007</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1527664039305757</v>
+        <v>-0.3520763880373683</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.64096564444054</v>
+        <v>2.832094333593933</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748282241030429</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.734498962723486</v>
+        <v>3.045213642340955</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.865398924600707</v>
+        <v>-4.13906409086047</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.187982968569456</v>
+        <v>1.38923158168302</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1042033517095455</v>
+        <v>-0.3035133358163381</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.671976951697759</v>
+        <v>2.863105640851153</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721073619942741</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.729574671235209</v>
+        <v>3.040289350852678</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.752727706364457</v>
+        <v>-4.02639287262422</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.228127164375679</v>
+        <v>1.429375777489243</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.00846786652670467</v>
+        <v>-0.1908421175800879</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.734655391151232</v>
+        <v>2.925784080304626</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743044028268539</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.735065967065876</v>
+        <v>3.045780646683345</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.640350705181784</v>
+        <v>-3.914015871441547</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.278569260679415</v>
+        <v>1.479817873792979</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.00846786652670467</v>
+        <v>-0.1908421175800879</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.7401466869819</v>
+        <v>2.931275376135293</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689594264968864</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.746563168834415</v>
+        <v>3.057277848451884</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.838585274068515</v>
+        <v>-4.112250440328277</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.210772634893262</v>
+        <v>1.412021248006826</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1897667023600259</v>
+        <v>-0.3890766864668185</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.6327031474184</v>
+        <v>2.823831836571793</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643066046175324</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.584918888835069</v>
+        <v>2.895633568452538</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.921586555093794</v>
+        <v>-4.195251721353556</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.015927842483804</v>
+        <v>1.217176455597368</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2083375868871997</v>
+        <v>-0.4076475709939922</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.459916336702749</v>
+        <v>2.651045025856142</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682712735199271</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.705068549554274</v>
+        <v>3.015783229171743</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.762392283037217</v>
+        <v>-4.03605744929698</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.19975521202564</v>
+        <v>1.401003825139204</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2083375868871997</v>
+        <v>-0.4076475709939922</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.580065997421955</v>
+        <v>2.771194686575348</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733008865660771</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.719581575656597</v>
+        <v>3.030296255274066</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.84899086601832</v>
+        <v>-4.122656032278083</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.179628804935522</v>
+        <v>1.380877418049086</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2083375868871997</v>
+        <v>-0.4076475709939922</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.594579023524278</v>
+        <v>2.785707712677671</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741170494383426</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.717001016998966</v>
+        <v>3.027715696616435</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.810607203460169</v>
+        <v>-4.084272369719931</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.192401711301151</v>
+        <v>1.393650324414715</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1699539243290485</v>
+        <v>-0.3692639084358411</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.615028662401537</v>
+        <v>2.806157351554931</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751143622002486</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.713730045844268</v>
+        <v>3.024444725461737</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.633490873425003</v>
+        <v>-3.907156039684765</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.259977272160519</v>
+        <v>1.461225885274083</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1699539243290485</v>
+        <v>-0.3692639084358411</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.611757691246839</v>
+        <v>2.802886380400233</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741324873263904</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.714413437606181</v>
+        <v>3.02512811722365</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.60378874944871</v>
+        <v>-3.922382923512446</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.27254151351295</v>
+        <v>1.455818523504924</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1744240495443619</v>
+        <v>-0.3999088099459803</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.609759007879564</v>
+        <v>2.785182831256062</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481238</v>
+        <v>3.750725801481237</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.708200412912595</v>
+        <v>3.018915092530064</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.424413328209941</v>
+        <v>-3.743007502273678</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.338078657314872</v>
+        <v>1.521355667306846</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.01764729137364318</v>
+        <v>-0.2431320517752616</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.69761203808841</v>
+        <v>2.873035861464908</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452233</v>
+        <v>3.716988143452232</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.689007868244185</v>
+        <v>2.999722547861654</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.469427541730548</v>
+        <v>-3.788021715794284</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.300880427238219</v>
+        <v>1.484157437230193</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.04799618668824779</v>
+        <v>-0.2734809470898663</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.660210156231237</v>
+        <v>2.835633979607735</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702303297954</v>
+        <v>3.737023032979539</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.694699430583131</v>
+        <v>3.0054141102006</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.736432052002983</v>
+        <v>-4.05502622606672</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.19977018546819</v>
+        <v>1.383047195460165</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2423592247311964</v>
+        <v>-0.4678439851328148</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.549283895744413</v>
+        <v>2.724707719120911</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230587923081</v>
+        <v>3.702305879230809</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.693903352479632</v>
+        <v>3.004618032097101</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.025219272461898</v>
+        <v>-4.343813446525635</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.083459219181126</v>
+        <v>1.2667362291731</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3434453448301967</v>
+        <v>-0.5689301052318152</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.487836145581515</v>
+        <v>2.663259968958013</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285456</v>
+        <v>3.705568086285455</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.691503314033949</v>
+        <v>3.002217993651418</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.992743686291126</v>
+        <v>-4.311337860354863</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.094049415203751</v>
+        <v>1.277326425195725</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3434453448301967</v>
+        <v>-0.5689301052318152</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.485436107135831</v>
+        <v>2.660859930512329</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848104</v>
+        <v>3.709506867848103</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.688028033242194</v>
+        <v>2.998742712859663</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.973705558583829</v>
+        <v>-4.292299732647566</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.098189385494915</v>
+        <v>1.281466395486889</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4016289561613913</v>
+        <v>-0.6271137165630097</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.44705065954536</v>
+        <v>2.622474482921857</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731060897601253</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.865609902180875</v>
+        <v>3.176324581798343</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.990451423840204</v>
+        <v>-4.309045597903941</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.269072908331046</v>
+        <v>1.45234991832302</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4016289561613913</v>
+        <v>-0.6271137165630097</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.62463252848404</v>
+        <v>2.800056351860538</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722443786537865</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.866443231167008</v>
+        <v>3.177157910784477</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.042771804440996</v>
+        <v>-4.361365978504733</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.248978085076863</v>
+        <v>1.432255095068837</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3666820961525191</v>
+        <v>-0.5921668565541376</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.646433973475497</v>
+        <v>2.821857796851995</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787422005259124</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.872451761563934</v>
+        <v>3.183166441181403</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.187094710365915</v>
+        <v>-4.505688884429651</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.197257453103821</v>
+        <v>1.380534463095795</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3666820961525191</v>
+        <v>-0.5921668565541376</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.652442503872423</v>
+        <v>2.827866327248921</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781497674989909</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.951604409355956</v>
+        <v>3.262319088973425</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.039351740130912</v>
+        <v>-4.357945914194649</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.335507288989844</v>
+        <v>1.518784298981818</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.198874738917636</v>
+        <v>-0.4243594993192544</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.832279566005375</v>
+        <v>3.007703389381872</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.825765278950782</v>
+        <v>3.749257754996581</v>
       </c>
       <c r="C1967" t="n">
-        <v>3.033370389674982</v>
+        <v>2.907117293589092</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.039351740130912</v>
+        <v>-4.313566827722202</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.335507288989844</v>
+        <v>1.181334138186464</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.198874738917636</v>
+        <v>-0.4243594993192544</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.02643418666135</v>
+        <v>2.652501593997539</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240517.xlsx
+++ b/tame_output/ON/bt/strategyON_20240517.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,22 +824,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-16.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.8%</t>
+          <t>-76.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.3%</t>
+          <t>110.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>129.5%</t>
+          <t>128.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.7%</t>
+          <t>-51.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-72.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.2%</t>
+          <t>448.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-10.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-592.9%</t>
+          <t>-573.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,27 +1155,27 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-40.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>140.2%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-258.1%</t>
+          <t>-245.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.9%</t>
+          <t>-26.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.8%</t>
+          <t>-30.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.8%</t>
+          <t>-20.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-144.6%</t>
+          <t>-93.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-266.4%</t>
+          <t>-247.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.5%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-180.8%</t>
+          <t>-164.8%</t>
         </is>
       </c>
     </row>
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
-        <v>3.426155199561141</v>
+        <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
         <v>-6.511197498137381</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.8213197759924413</v>
+        <v>0.510605096374972</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.488936960400945</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.532793023320575</v>
+        <v>2.222078343703105</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
-        <v>3.421340632032601</v>
+        <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.924179982278475</v>
+        <v>-6.792738679286736</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.6513122148074637</v>
+        <v>0.3931740563866906</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.488936960400945</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.527978455792035</v>
+        <v>2.217263776174566</v>
       </c>
     </row>
     <row r="1866">
@@ -44466,19 +44466,19 @@
         <v>3.305023265108639</v>
       </c>
       <c r="C1866" t="n">
-        <v>3.419334682641479</v>
+        <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.340571856565473</v>
+        <v>-7.209130553573734</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.482749515701542</v>
+        <v>0.2246113572807689</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.488936960400945</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.525972506400912</v>
+        <v>2.215257826783443</v>
       </c>
     </row>
     <row r="1867">
@@ -44489,19 +44489,19 @@
         <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
-        <v>3.429593373310158</v>
+        <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.717248867095317</v>
+        <v>-7.585807564103578</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.3423374021582832</v>
+        <v>0.08419924373751009</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.488936960400945</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.536231197069591</v>
+        <v>2.225516517452122</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
-        <v>3.425692938455853</v>
+        <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.063123689080125</v>
+        <v>-7.931682386088386</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.200087038510055</v>
+        <v>-0.0580511199107181</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.488936960400945</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.532330762215286</v>
+        <v>2.221616082597818</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
-        <v>3.424097858510854</v>
+        <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.22670356726451</v>
+        <v>-8.095262264272771</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.1330600072913026</v>
+        <v>-0.125078151129471</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.488936960400945</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.530735682270287</v>
+        <v>2.220021002652818</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.424633354969595</v>
       </c>
       <c r="C1870" t="n">
-        <v>3.427876834440062</v>
+        <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.523364909074708</v>
+        <v>-8.391923606082969</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.01817444649643152</v>
+        <v>-0.2399637119243421</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.557680096134823</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.493268776759168</v>
+        <v>2.182554097141699</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923088</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
-        <v>3.423850529905659</v>
+        <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.646609298290137</v>
+        <v>-8.515167995298398</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.0351496137241436</v>
+        <v>-0.2932877721449167</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.489242472224765</v>
+        <v>2.178527792607296</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
-        <v>3.423748428584075</v>
+        <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.029610687032768</v>
+        <v>-8.898169384041029</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.18845227054278</v>
+        <v>-0.4465904289635532</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.489140370903181</v>
+        <v>2.178425691285712</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
-        <v>3.426319944555505</v>
+        <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.187009567245889</v>
+        <v>-9.05556826425415</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.2488403066565983</v>
+        <v>-0.5069784650773714</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.715078976347944</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.397272558746739</v>
+        <v>2.08655787912927</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
-        <v>3.431670247853555</v>
+        <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.546539889749891</v>
+        <v>-9.415098586758152</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.3873021323601487</v>
+        <v>-0.6454402907809218</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.715078976347944</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.402622862044788</v>
+        <v>2.09190818242732</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
-        <v>3.439586267810733</v>
+        <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.596888953204113</v>
+        <v>-9.465447650212374</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.3995257377846602</v>
+        <v>-0.6576638962054333</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.765428039802166</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.380329443929433</v>
+        <v>2.069614764311964</v>
       </c>
     </row>
     <row r="1876">
@@ -44696,19 +44696,19 @@
         <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
-        <v>3.442628018432501</v>
+        <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.81603792127831</v>
+        <v>-9.684596618286571</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.4841435743925699</v>
+        <v>-0.7422817328133435</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.984577007876364</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.251881813706683</v>
+        <v>1.941167134089214</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.442628018432501</v>
+        <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.812346996321899</v>
+        <v>-9.68090569333016</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.482667204410006</v>
+        <v>-0.7408053628307791</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.984577007876364</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.251881813706683</v>
+        <v>1.941167134089214</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.448141215551144</v>
+        <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.01660517165176</v>
+        <v>-9.885163868660024</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.5588572774233089</v>
+        <v>-0.8169954358440821</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.112215952490353</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.180811644056933</v>
+        <v>1.870096964439463</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.45262377003558</v>
+        <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.23464294328294</v>
+        <v>-10.1032016402912</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.6415898315913435</v>
+        <v>-0.8997279900121176</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.286986720586252</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.080431737683829</v>
+        <v>1.76971705806636</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.467995471529001</v>
+        <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.16117311161549</v>
+        <v>-10.02973180862375</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.5968301974309433</v>
+        <v>-0.8549683558517165</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.213516888918803</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.139885338177719</v>
+        <v>1.82917065856025</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078599</v>
+        <v>3.4900556660786</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.482550692276518</v>
+        <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.33629752900204</v>
+        <v>-10.2048562260103</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.6523247436380437</v>
+        <v>-0.9104629020588169</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.388641306305347</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.04936590849331</v>
+        <v>1.738651228875841</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.485875018880273</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.475331527374922</v>
+        <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.57074962301652</v>
+        <v>-10.43930832002479</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.7533247461454358</v>
+        <v>-1.011462904566209</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.388641306305347</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.042146743591714</v>
+        <v>1.731432063974245</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234398</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.468659336600945</v>
+        <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.85855346755376</v>
+        <v>-10.72711216456202</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.875118474734307</v>
+        <v>-1.13325663315508</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.676445150842585</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.862792246095395</v>
+        <v>1.552077566477926</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.469775126439502</v>
+        <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.91133962315409</v>
+        <v>-10.77989832016235</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.8951171471358812</v>
+        <v>-1.153255305556655</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.772120637424982</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.806502743984513</v>
+        <v>1.495788064367044</v>
       </c>
     </row>
     <row r="1885">
@@ -44903,19 +44903,19 @@
         <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.472468855068616</v>
+        <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.14336854289035</v>
+        <v>-11.01192723989861</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.9852349864012715</v>
+        <v>-1.243373144822045</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.834133334613405</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.771988854300574</v>
+        <v>1.461274174683105</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.476459190755017</v>
+        <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.09135302892154</v>
+        <v>-10.9599117259298</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.9604384451273456</v>
+        <v>-1.218576603548119</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.834133334613405</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.775979189986974</v>
+        <v>1.465264510369505</v>
       </c>
     </row>
     <row r="1887">
@@ -44949,19 +44949,19 @@
         <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.474983963856276</v>
+        <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.23302487064566</v>
+        <v>-11.10158356765392</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.018582408715735</v>
+        <v>-1.276720567136508</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.834133334613405</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.774503963088233</v>
+        <v>1.463789283470764</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.490037374021148</v>
+        <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.18343402622082</v>
+        <v>-11.05199272322909</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.9836926607809295</v>
+        <v>-1.241830819201703</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.784542490188572</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.819311879908005</v>
+        <v>1.508597200290536</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.476986240374465</v>
+        <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.98428191898373</v>
+        <v>-10.85284061599199</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.9170829515327727</v>
+        <v>-1.175221109953546</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.619219964238758</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.90545426183121</v>
+        <v>1.594739582213741</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.486565313410674</v>
+        <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.75843676626431</v>
+        <v>-10.62699546327257</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.817165817408799</v>
+        <v>-1.075303975829573</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.577293288651595</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.940189340219717</v>
+        <v>1.629474660602248</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.487704457966732</v>
+        <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.63385810992672</v>
+        <v>-10.50241680693498</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.7661952103177039</v>
+        <v>-1.024333368738477</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.577293288651595</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.941328484775776</v>
+        <v>1.630613805158307</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116215</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.49033823212884</v>
+        <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.68675339797101</v>
+        <v>-10.55531209497927</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.7847195513733105</v>
+        <v>-1.042857709794084</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.572337942563149</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.946935466590952</v>
+        <v>1.636220786973482</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.496071936367477</v>
+        <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.40284466704226</v>
+        <v>-10.27140336405052</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.6654223547631748</v>
+        <v>-0.9235605131839479</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.572337942563149</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.952669170829588</v>
+        <v>1.641954491212119</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425327</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.486334673973611</v>
+        <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.33147827443261</v>
+        <v>-10.20003697144087</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.6466130601131805</v>
+        <v>-0.9047512185339546</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.500971549953501</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.985751744001512</v>
+        <v>1.675037064384042</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.476451192660704</v>
+        <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.06764140722854</v>
+        <v>-9.936200104236804</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.5509617945444609</v>
+        <v>-0.8090999529652341</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.500971549953501</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.975868262688603</v>
+        <v>1.665153583071135</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.47461663216133</v>
+        <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.800399606360145</v>
+        <v>-9.668958303368406</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.4458996346964752</v>
+        <v>-0.7040377931172483</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.500971549953501</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.97403370218923</v>
+        <v>1.663319022571761</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781946</v>
+        <v>3.784680945781948</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.474316317187869</v>
+        <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.702492567683654</v>
+        <v>-9.571051264691915</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.40703713419934</v>
+        <v>-0.6651752926201131</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.432985800092944</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.014524837132103</v>
+        <v>1.703810157514634</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567243</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.474984823333363</v>
+        <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.678539026707696</v>
+        <v>-9.547097723715957</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.396787211663463</v>
+        <v>-0.6549253700842361</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.409032259116987</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.029565467863171</v>
+        <v>1.718850788245702</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78930753648777</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.461724507171611</v>
+        <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.414479088384899</v>
+        <v>-9.28303778539316</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.3044235524960963</v>
+        <v>-0.5625617109168699</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.144972320794191</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.174741114695097</v>
+        <v>1.864026435077628</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309724</v>
+        <v>3.833249172309726</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.45893747351131</v>
+        <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.707399464880062</v>
+        <v>-8.575958161888323</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.02437873675446234</v>
+        <v>-0.2825168951752355</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.144972320794191</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.171954081034796</v>
+        <v>1.861239401417327</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858727</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.459281097399151</v>
+        <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.667215166513872</v>
+        <v>-8.535773863522133</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.007961393520144799</v>
+        <v>-0.2660995519409179</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.104788022428</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.196408283942351</v>
+        <v>1.885693604324883</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096472</v>
+        <v>3.856158176096474</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.458647918619908</v>
+        <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.587145370976067</v>
+        <v>-8.455704067984328</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.02343334591573409</v>
+        <v>-0.2347048125050395</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.024718226890196</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.243816982485791</v>
+        <v>1.933102302868322</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.78732685376181</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.466572347457761</v>
+        <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.353664148746468</v>
+        <v>-8.222222845754729</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.1247502636454261</v>
+        <v>-0.1333878947753471</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.791237004660597</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.391830144661403</v>
+        <v>2.081115465043934</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255787</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.463680137144801</v>
+        <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.203997757738954</v>
+        <v>-8.072556454747215</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.1817246097354728</v>
+        <v>-0.07641354868530081</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.698333513418061</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.444680029093965</v>
+        <v>2.133965349476496</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860428</v>
+        <v>3.76317867286043</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.459047623891828</v>
+        <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.071722284108066</v>
+        <v>-7.940280981116328</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2300022859348547</v>
+        <v>-0.02813587248591931</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.566058039787175</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.519412800019524</v>
+        <v>2.208698120402055</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575955</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.461862684579465</v>
+        <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.881122609434914</v>
+        <v>-7.749681306443176</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3090572164917522</v>
+        <v>0.05091905807097863</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.375458365114022</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.636587665511052</v>
+        <v>2.325872985893583</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430989</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.474769025803124</v>
+        <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.632122810751333</v>
+        <v>-7.500681507759595</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4215634771888435</v>
+        <v>0.1634253187680699</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.375458365114022</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.649494006734711</v>
+        <v>2.338779327117242</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.346793096203905</v>
+        <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.737712800524437</v>
+        <v>-7.606271497532699</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2513515516803828</v>
+        <v>-0.006786606740390777</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.481048354887126</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.45816408327163</v>
+        <v>2.147449403654161</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.395337438080992</v>
+        <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.756447702643034</v>
+        <v>-7.625006399651296</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2924019327100305</v>
+        <v>0.03426377428925687</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.481048354887126</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.506708425148716</v>
+        <v>2.195993745531247</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
-        <v>3.275458515392824</v>
+        <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.608507661235435</v>
+        <v>-7.477066358243697</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2316990265849026</v>
+        <v>-0.02643913183587099</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.460727438978569</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.399022052005683</v>
+        <v>2.088307372388214</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879202</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
-        <v>3.266744529139346</v>
+        <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.584279024846462</v>
+        <v>-7.452837721854724</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2326764948870137</v>
+        <v>-0.02546166353376034</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.436498802589596</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.404845247585588</v>
+        <v>2.094130567968119</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568109</v>
       </c>
       <c r="C1912" t="n">
-        <v>3.259783917044253</v>
+        <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.540730618075772</v>
+        <v>-7.409289315084034</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2431352455001967</v>
+        <v>-0.01500291292057732</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.436498802589596</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.397884635490495</v>
+        <v>2.087169955873026</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963419</v>
+        <v>3.782918957963421</v>
       </c>
       <c r="C1913" t="n">
-        <v>3.274246271425396</v>
+        <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.298582224621914</v>
+        <v>-7.167140921630176</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3544569572628831</v>
+        <v>0.09631879884210903</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.436498802589596</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.412346989871638</v>
+        <v>2.101632310254169</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192819</v>
       </c>
       <c r="C1914" t="n">
-        <v>3.268778391884591</v>
+        <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.235352852853565</v>
+        <v>-7.103911549861827</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3742808264294171</v>
+        <v>0.1161426680086435</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.436498802589596</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.406879110330833</v>
+        <v>2.096164430713364</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
-        <v>3.266276485895168</v>
+        <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.112061718036434</v>
+        <v>-6.980620415044696</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4210953743668466</v>
+        <v>0.1629572159460726</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.313207667772466</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.478351885231688</v>
+        <v>2.167637205614219</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389911</v>
       </c>
       <c r="C1916" t="n">
-        <v>3.273977464132493</v>
+        <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.090912519132991</v>
+        <v>-6.959471216141253</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.437256032165549</v>
+        <v>0.1791178737447754</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.292058468869023</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.49874238281108</v>
+        <v>2.188027703193611</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788094</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
-        <v>3.269758172479543</v>
+        <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.847147077149547</v>
+        <v>-6.715705774157809</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5305429173059775</v>
+        <v>0.2724047588852039</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.292058468869023</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.49452309115813</v>
+        <v>2.183808411540661</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527527</v>
       </c>
       <c r="C1918" t="n">
-        <v>3.271882486399559</v>
+        <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.700250049431677</v>
+        <v>-6.568808746439938</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5914260423131412</v>
+        <v>0.3332878838923681</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.244400226890435</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.525242350265299</v>
+        <v>2.21452767064783</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.826351398749185</v>
       </c>
       <c r="C1919" t="n">
-        <v>3.264624561383262</v>
+        <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.450399655482602</v>
+        <v>-6.318958352490863</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6841082748764733</v>
+        <v>0.4259701164557002</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.244400226890435</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.517984425249001</v>
+        <v>2.207269745631532</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481497</v>
       </c>
       <c r="C1920" t="n">
-        <v>3.26822368490391</v>
+        <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.27450756301517</v>
+        <v>-6.143066260023431</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.758064235384095</v>
+        <v>0.4999260769633214</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.244400226890435</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.52158354876965</v>
+        <v>2.210868869152181</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.780930335862988</v>
       </c>
       <c r="C1921" t="n">
-        <v>3.281551190958464</v>
+        <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.103061099992707</v>
+        <v>-5.971619797000968</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8399703266476339</v>
+        <v>0.5818321682268608</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.072953763867972</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.637778932637681</v>
+        <v>2.327064253020212</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
-        <v>3.280571668574761</v>
+        <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.878028100323884</v>
+        <v>-5.746586797332145</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.92900400413146</v>
+        <v>0.6708658457106869</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.8479207641991487</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.771819210055272</v>
+        <v>2.461104530437803</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.764614304353074</v>
       </c>
       <c r="C1923" t="n">
-        <v>3.285266469629078</v>
+        <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.814392358089949</v>
+        <v>-5.682951055098211</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9591531020793513</v>
+        <v>0.7010149436585777</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.7842850219652142</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.81469545644995</v>
+        <v>2.503980776832481</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.798811195544783</v>
       </c>
       <c r="C1924" t="n">
-        <v>3.266460728412874</v>
+        <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.721392316884051</v>
+        <v>-5.589951013892312</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9775473773455063</v>
+        <v>0.7194092189247328</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.7842850219652142</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.795889715233746</v>
+        <v>2.485175035616277</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.797691308712294</v>
       </c>
       <c r="C1925" t="n">
-        <v>3.268203805037751</v>
+        <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.642484528317248</v>
+        <v>-5.349520517087452</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.010853569397105</v>
+        <v>0.8173244942715545</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7053772333984109</v>
+        <v>-0.5438545251603539</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.844977464998705</v>
+        <v>2.63117641032407</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837683</v>
+        <v>3.821589933837685</v>
       </c>
       <c r="C1926" t="n">
-        <v>3.272133118872572</v>
+        <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.570241960146054</v>
+        <v>-5.277277948916257</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.043679910500403</v>
+        <v>0.8501508353748526</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7053772333984109</v>
+        <v>-0.5438545251603539</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.848906778833525</v>
+        <v>2.63510572415889</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349965</v>
+        <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
-        <v>3.272811702789912</v>
+        <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.454302110520868</v>
+        <v>-5.161338099291072</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.090734434267817</v>
+        <v>0.8972053591422666</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.628555502382287</v>
+        <v>-0.46703279414423</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.89567840136054</v>
+        <v>2.681877346685905</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972339</v>
+        <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
-        <v>3.269809774009905</v>
+        <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.211646522097706</v>
+        <v>-4.918682510867908</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.184794740857075</v>
+        <v>0.9912656657315255</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.628555502382287</v>
+        <v>-0.46703279414423</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.892676472580533</v>
+        <v>2.678875417905898</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.81866537614594</v>
       </c>
       <c r="C1929" t="n">
-        <v>3.271388811020519</v>
+        <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.991625724060695</v>
+        <v>-4.698661712830898</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.274382097082494</v>
+        <v>1.080853021956944</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4873356573143067</v>
+        <v>-0.3258129490762498</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.978987416631935</v>
+        <v>2.7651863619573</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327095200995</v>
+        <v>3.843270952009952</v>
       </c>
       <c r="C1930" t="n">
-        <v>3.287282993822342</v>
+        <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.858758034997417</v>
+        <v>-4.56579402376762</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.343423355509628</v>
+        <v>1.149894280384078</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4873356573143067</v>
+        <v>-0.3258129490762498</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.994881599433759</v>
+        <v>2.781080544759124</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504381096626</v>
+        <v>3.845043810966262</v>
       </c>
       <c r="C1931" t="n">
-        <v>3.288428838262644</v>
+        <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.699242931478048</v>
+        <v>-4.40627892024825</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.408375241357678</v>
+        <v>1.214846166232128</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3278205537949368</v>
+        <v>-0.1662978455568799</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.091736505985683</v>
+        <v>2.877935451311048</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046998</v>
+        <v>3.791269976046999</v>
       </c>
       <c r="C1932" t="n">
-        <v>3.298516940824084</v>
+        <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.55457078637831</v>
+        <v>-4.261606775148513</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.476332201959013</v>
+        <v>1.282803126833463</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1831484086951994</v>
+        <v>-0.02162570045714246</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.188627895606965</v>
+        <v>2.97482684093233</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412106</v>
+        <v>3.735835647412108</v>
       </c>
       <c r="C1933" t="n">
-        <v>3.28455443222551</v>
+        <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.614445613736002</v>
+        <v>-4.321481602506205</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.438419762417362</v>
+        <v>1.244890687291812</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2430232360528915</v>
+        <v>-0.08150052781483458</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.138740490593775</v>
+        <v>2.924939435919141</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144517</v>
+        <v>3.762643902144519</v>
       </c>
       <c r="C1934" t="n">
-        <v>3.306954925548076</v>
+        <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.527646115956994</v>
+        <v>-4.234682104727197</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.495540054851531</v>
+        <v>1.302010979725981</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2430232360528915</v>
+        <v>-0.08150052781483458</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.161140983916341</v>
+        <v>2.947339929241707</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900695</v>
+        <v>3.729142822900696</v>
       </c>
       <c r="C1935" t="n">
-        <v>3.307027326921488</v>
+        <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.5301158224188</v>
+        <v>-4.237151811189003</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.494624573640221</v>
+        <v>1.301095498514671</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2454929425146977</v>
+        <v>-0.08397023427664074</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.15973156141267</v>
+        <v>2.945930506738035</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473602</v>
+        <v>3.743216620473603</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.31803424939619</v>
+        <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.59848600874281</v>
+        <v>-4.305521997513013</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.478283421585319</v>
+        <v>1.284754346459769</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2362172434784827</v>
+        <v>-0.0746945352404258</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.176303903309101</v>
+        <v>2.962502848634466</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978371</v>
+        <v>3.714175563978372</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.308470958028082</v>
+        <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.477069579116334</v>
+        <v>-4.184105567886537</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.517286702067801</v>
+        <v>1.323757626942251</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2362172434784827</v>
+        <v>-0.0746945352404258</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.166740611940992</v>
+        <v>2.952939557266357</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887703</v>
+        <v>3.710903155887705</v>
       </c>
       <c r="C1938" t="n">
-        <v>3.133180523068468</v>
+        <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.508062738445039</v>
+        <v>-4.215098727215242</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.329599003376706</v>
+        <v>1.136069928251155</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2362172434784827</v>
+        <v>-0.0746945352404258</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.991450176981379</v>
+        <v>2.777649122306744</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.7460389506759</v>
+        <v>3.746038950675903</v>
       </c>
       <c r="C1939" t="n">
-        <v>3.137747755060256</v>
+        <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.332588478652569</v>
+        <v>-4.039624467422772</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.404355939285481</v>
+        <v>1.210826864159931</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2362172434784827</v>
+        <v>-0.0746945352404258</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.996017408973167</v>
+        <v>2.782216354298532</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695446</v>
+        <v>3.765020747695448</v>
       </c>
       <c r="C1940" t="n">
-        <v>3.113489783821463</v>
+        <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.443524731293818</v>
+        <v>-4.150560720064021</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.335723466990189</v>
+        <v>1.142194391864638</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2362172434784827</v>
+        <v>-0.0746945352404258</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.971759437734374</v>
+        <v>2.757958383059739</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581293</v>
+        <v>3.773206721581294</v>
       </c>
       <c r="C1941" t="n">
-        <v>3.116621169041369</v>
+        <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.646551308837052</v>
+        <v>-4.353587297607254</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.257644221192801</v>
+        <v>1.064115146067251</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.4392438210217161</v>
+        <v>-0.2777211127836592</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.85307487642834</v>
+        <v>2.639273821753704</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734162</v>
+        <v>3.784340376734164</v>
       </c>
       <c r="C1942" t="n">
-        <v>3.126793555473501</v>
+        <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.488625709901759</v>
+        <v>-4.195661698671961</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.33098684719905</v>
+        <v>1.1374577720735</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.4392438210217161</v>
+        <v>-0.2777211127836592</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.863247262860472</v>
+        <v>2.649446208185837</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212299</v>
+        <v>3.7869463822123</v>
       </c>
       <c r="C1943" t="n">
-        <v>3.121739826047361</v>
+        <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.402382246875381</v>
+        <v>-4.109418235645584</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.360430502983462</v>
+        <v>1.166901427857912</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.4392438210217161</v>
+        <v>-0.2777211127836592</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.858193533434332</v>
+        <v>2.644392478759698</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786046</v>
+        <v>3.752023923786048</v>
       </c>
       <c r="C1944" t="n">
-        <v>3.113515601491887</v>
+        <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.403565331526442</v>
+        <v>-4.110601320296645</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.351733044567563</v>
+        <v>1.158203969442013</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.4448868694882276</v>
+        <v>-0.2833641612501707</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.846583479798951</v>
+        <v>2.632782425124316</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273192</v>
+        <v>3.753567590273194</v>
       </c>
       <c r="C1945" t="n">
-        <v>3.114067474524989</v>
+        <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.280437624532359</v>
+        <v>-3.987473613302562</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.401536000398298</v>
+        <v>1.208006925272747</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.4448868694882276</v>
+        <v>-0.2833641612501707</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.847135352832052</v>
+        <v>2.633334298157417</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279502</v>
+        <v>3.733387025279503</v>
       </c>
       <c r="C1946" t="n">
-        <v>3.043340166416354</v>
+        <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.1876271430815</v>
+        <v>-3.894663131851703</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.367932884870007</v>
+        <v>1.174403809744457</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3520763880373683</v>
+        <v>-0.1905536797993114</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.832094333593933</v>
+        <v>2.618293278919299</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030429</v>
+        <v>3.748282241030431</v>
       </c>
       <c r="C1947" t="n">
-        <v>3.045213642340955</v>
+        <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.13906409086047</v>
+        <v>-3.846100079630673</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.38923158168302</v>
+        <v>1.19570250655747</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3035133358163381</v>
+        <v>-0.1419906275782812</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.863105640851153</v>
+        <v>2.649304586176518</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942741</v>
+        <v>3.721073619942743</v>
       </c>
       <c r="C1948" t="n">
-        <v>3.040289350852678</v>
+        <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.02639287262422</v>
+        <v>-3.733428861394422</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.429375777489243</v>
+        <v>1.235846702363693</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1908421175800879</v>
+        <v>-0.02931940934203098</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.925784080304626</v>
+        <v>2.711983025629991</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268539</v>
+        <v>3.743044028268541</v>
       </c>
       <c r="C1949" t="n">
-        <v>3.045780646683345</v>
+        <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.914015871441547</v>
+        <v>-3.62105186021175</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.479817873792979</v>
+        <v>1.286288798667429</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1908421175800879</v>
+        <v>-0.02931940934203098</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.931275376135293</v>
+        <v>2.717474321460658</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968864</v>
+        <v>3.689594264968866</v>
       </c>
       <c r="C1950" t="n">
-        <v>3.057277848451884</v>
+        <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.112250440328277</v>
+        <v>-3.81928642909848</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.412021248006826</v>
+        <v>1.218492172881276</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.3890766864668185</v>
+        <v>-0.2275539782287616</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.823831836571793</v>
+        <v>2.610030781897159</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175324</v>
+        <v>3.643066046175326</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.895633568452538</v>
+        <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.195251721353556</v>
+        <v>-3.902287710123759</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.217176455597368</v>
+        <v>1.023647380471818</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.4076475709939922</v>
+        <v>-0.2461248627559353</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.651045025856142</v>
+        <v>2.437243971181508</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199271</v>
+        <v>3.682712735199273</v>
       </c>
       <c r="C1952" t="n">
-        <v>3.015783229171743</v>
+        <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.03605744929698</v>
+        <v>-3.743093438067183</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.401003825139204</v>
+        <v>1.207474750013654</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.4076475709939922</v>
+        <v>-0.2461248627559353</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.771194686575348</v>
+        <v>2.557393631900713</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660771</v>
+        <v>3.733008865660772</v>
       </c>
       <c r="C1953" t="n">
-        <v>3.030296255274066</v>
+        <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.122656032278083</v>
+        <v>-3.829692021048286</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.380877418049086</v>
+        <v>1.187348342923536</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.4076475709939922</v>
+        <v>-0.2461248627559353</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.785707712677671</v>
+        <v>2.571906658003036</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383426</v>
+        <v>3.741170494383428</v>
       </c>
       <c r="C1954" t="n">
-        <v>3.027715696616435</v>
+        <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.084272369719931</v>
+        <v>-3.791308358490135</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.393650324414715</v>
+        <v>1.200121249289165</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.3692639084358411</v>
+        <v>-0.2077412001977841</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.806157351554931</v>
+        <v>2.592356296880296</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002486</v>
+        <v>3.751143622002489</v>
       </c>
       <c r="C1955" t="n">
-        <v>3.024444725461737</v>
+        <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.907156039684765</v>
+        <v>-3.614192028454969</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.461225885274083</v>
+        <v>1.267696810148533</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.3692639084358411</v>
+        <v>-0.2077412001977841</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.802886380400233</v>
+        <v>2.589085325725598</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263904</v>
+        <v>3.741324873263906</v>
       </c>
       <c r="C1956" t="n">
-        <v>3.02512811722365</v>
+        <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.922382923512446</v>
+        <v>-3.584489904478675</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.455818523504924</v>
+        <v>1.280261051500964</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.3999088099459803</v>
+        <v>-0.2122113254130975</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.785182831256062</v>
+        <v>2.587086642358323</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481237</v>
+        <v>3.75072580148124</v>
       </c>
       <c r="C1957" t="n">
-        <v>3.018915092530064</v>
+        <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.743007502273678</v>
+        <v>-3.405114483239907</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.521355667306846</v>
+        <v>1.345798195302885</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.2431320517752616</v>
+        <v>-0.05543456724237883</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.873035861464908</v>
+        <v>2.674939672567168</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452232</v>
+        <v>3.716988143452235</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.999722547861654</v>
+        <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.788021715794284</v>
+        <v>-3.450128696760513</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.484157437230193</v>
+        <v>1.308599965226233</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.2734809470898663</v>
+        <v>-0.08578346255698344</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.835633979607735</v>
+        <v>2.637537790709995</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979539</v>
+        <v>3.737023032979542</v>
       </c>
       <c r="C1959" t="n">
-        <v>3.0054141102006</v>
+        <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.05502622606672</v>
+        <v>-3.717133207032949</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.383047195460165</v>
+        <v>1.207489723456204</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.4678439851328148</v>
+        <v>-0.280146500599932</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.724707719120911</v>
+        <v>2.526611530223172</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230809</v>
+        <v>3.702305879230812</v>
       </c>
       <c r="C1960" t="n">
-        <v>3.004618032097101</v>
+        <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.343813446525635</v>
+        <v>-4.005920427491864</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.2667362291731</v>
+        <v>1.09117875716914</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.5689301052318152</v>
+        <v>-0.3812326206989324</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.663259968958013</v>
+        <v>2.465163780060273</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285455</v>
+        <v>3.705568086285457</v>
       </c>
       <c r="C1961" t="n">
-        <v>3.002217993651418</v>
+        <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.311337860354863</v>
+        <v>-3.973444841321092</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.277326425195725</v>
+        <v>1.101768953191765</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.5689301052318152</v>
+        <v>-0.3812326206989324</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.660859930512329</v>
+        <v>2.46276374161459</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848103</v>
+        <v>3.709506867848106</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.998742712859663</v>
+        <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.292299732647566</v>
+        <v>-3.954406713613794</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.281466395486889</v>
+        <v>1.105908923482929</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.6271137165630097</v>
+        <v>-0.4394162320301269</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.622474482921857</v>
+        <v>2.424378294024118</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601253</v>
+        <v>3.731060897601255</v>
       </c>
       <c r="C1963" t="n">
-        <v>3.176324581798343</v>
+        <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.309045597903941</v>
+        <v>-3.97115257887017</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.45234991832302</v>
+        <v>1.276792446319059</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.6271137165630097</v>
+        <v>-0.4394162320301269</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.800056351860538</v>
+        <v>2.601960162962799</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537865</v>
+        <v>3.722443786537867</v>
       </c>
       <c r="C1964" t="n">
-        <v>3.177157910784477</v>
+        <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.361365978504733</v>
+        <v>-4.023472959470961</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.432255095068837</v>
+        <v>1.256697623064876</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5921668565541376</v>
+        <v>-0.4044693720212548</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.821857796851995</v>
+        <v>2.623761607954255</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259124</v>
+        <v>3.787422005259126</v>
       </c>
       <c r="C1965" t="n">
-        <v>3.183166441181403</v>
+        <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.505688884429651</v>
+        <v>-4.16779586539588</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.380534463095795</v>
+        <v>1.204976991091835</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5921668565541376</v>
+        <v>-0.4044693720212548</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.827866327248921</v>
+        <v>2.629770138351181</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989909</v>
+        <v>3.7282787398688</v>
       </c>
       <c r="C1966" t="n">
-        <v>3.262319088973425</v>
+        <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.357945914194649</v>
+        <v>-4.020052895160878</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.518784298981818</v>
+        <v>1.343226826977858</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.4243594993192544</v>
+        <v>-0.2366620147863716</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.007703389381872</v>
+        <v>2.809607200484133</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.749257754996581</v>
+        <v>3.825757063511185</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.907117293589092</v>
+        <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.313566827722202</v>
+        <v>-4.122360838654295</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.181334138186464</v>
+        <v>1.305097271111972</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.4243594993192544</v>
+        <v>-0.2366620147863716</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.652501593997539</v>
+        <v>2.812400822015614</v>
       </c>
     </row>
   </sheetData>
